--- a/research/traditional_assets/database/data/norway/norway_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_electrical_equipment.xlsx
@@ -1650,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1787,22 +1787,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09347004797179444</v>
+        <v>0.09329951386625648</v>
       </c>
       <c r="C2">
-        <v>21.96098781067488</v>
+        <v>21.76872375419899</v>
       </c>
       <c r="D2">
-        <v>21.96098781067488</v>
+        <v>22.016823754199</v>
       </c>
       <c r="E2">
-        <v>-17.1</v>
+        <v>-16.8519</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2481</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1823,28 +1823,28 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01247943</v>
       </c>
       <c r="N2">
-        <v>0.2799999999999998</v>
+        <v>0.2675205699999998</v>
       </c>
       <c r="O2">
-        <v>0.06159999999999996</v>
+        <v>0.05885452539999995</v>
       </c>
       <c r="P2">
-        <v>0.2183999999999998</v>
+        <v>0.2086660445999998</v>
       </c>
       <c r="Q2">
-        <v>2.3984</v>
+        <v>2.3886660446</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09347004797179444</v>
+        <v>0.09384563016793585</v>
       </c>
       <c r="T2">
-        <v>1.100924895422504</v>
+        <v>1.109598849144015</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>22.43692219917094</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1869,22 +1869,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09329951386625648</v>
+        <v>0.09315237976071852</v>
       </c>
       <c r="C3">
-        <v>21.76872375419899</v>
+        <v>21.56902677756132</v>
       </c>
       <c r="D3">
-        <v>22.016823754199</v>
+        <v>22.06522677756132</v>
       </c>
       <c r="E3">
-        <v>-16.8519</v>
+        <v>-16.6038</v>
       </c>
       <c r="F3">
-        <v>0.2481</v>
+        <v>0.4962</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1905,45 +1905,45 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M3">
-        <v>0.01247943</v>
+        <v>0.02570316</v>
       </c>
       <c r="N3">
-        <v>0.2675205699999998</v>
+        <v>0.2542968399999998</v>
       </c>
       <c r="O3">
-        <v>0.05885452539999995</v>
+        <v>0.05594530479999996</v>
       </c>
       <c r="P3">
-        <v>0.2086660445999998</v>
+        <v>0.1983515351999998</v>
       </c>
       <c r="Q3">
-        <v>2.3886660446</v>
+        <v>2.3783515352</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09384563016793585</v>
+        <v>0.09422887730685564</v>
       </c>
       <c r="T3">
-        <v>1.109598849144015</v>
+        <v>1.11844982232923</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y3">
-        <v>22.43692219917094</v>
+        <v>10.89360218743531</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09315237976071852</v>
+        <v>0.09305204565518059</v>
       </c>
       <c r="C4">
-        <v>21.56902677756132</v>
+        <v>21.35405613571152</v>
       </c>
       <c r="D4">
-        <v>22.06522677756132</v>
+        <v>22.09835613571152</v>
       </c>
       <c r="E4">
-        <v>-16.6038</v>
+        <v>-16.3557</v>
       </c>
       <c r="F4">
-        <v>0.4962</v>
+        <v>0.7443000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1987,45 +1987,45 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M4">
-        <v>0.02570316</v>
+        <v>0.04041549000000001</v>
       </c>
       <c r="N4">
-        <v>0.2542968399999998</v>
+        <v>0.2395845099999998</v>
       </c>
       <c r="O4">
-        <v>0.05594530479999996</v>
+        <v>0.05270859219999996</v>
       </c>
       <c r="P4">
-        <v>0.1983515351999998</v>
+        <v>0.1868759177999998</v>
       </c>
       <c r="Q4">
-        <v>2.3783515352</v>
+        <v>2.3668759178</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09422887730685564</v>
+        <v>0.09462002644863979</v>
       </c>
       <c r="T4">
-        <v>1.11844982232923</v>
+        <v>1.127483289806924</v>
       </c>
       <c r="U4">
-        <v>0.0518</v>
+        <v>0.0543</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.040404</v>
+        <v>0.042354</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y4">
-        <v>10.89360218743531</v>
+        <v>6.928036750265796</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2033,22 +2033,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09305204565518059</v>
+        <v>0.09294391154964263</v>
       </c>
       <c r="C5">
-        <v>21.35405613571152</v>
+        <v>21.1417725435395</v>
       </c>
       <c r="D5">
-        <v>22.09835613571152</v>
+        <v>22.1341725435395</v>
       </c>
       <c r="E5">
-        <v>-16.3557</v>
+        <v>-16.1076</v>
       </c>
       <c r="F5">
-        <v>0.7443000000000001</v>
+        <v>0.9924000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2069,45 +2069,45 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M5">
-        <v>0.04041549000000001</v>
+        <v>0.05487972000000001</v>
       </c>
       <c r="N5">
-        <v>0.2395845099999998</v>
+        <v>0.2251202799999998</v>
       </c>
       <c r="O5">
-        <v>0.05270859219999996</v>
+        <v>0.04952646159999995</v>
       </c>
       <c r="P5">
-        <v>0.1868759177999998</v>
+        <v>0.1755938183999998</v>
       </c>
       <c r="Q5">
-        <v>2.3668759178</v>
+        <v>2.3555938184</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09462002644863979</v>
+        <v>0.09501932453087775</v>
       </c>
       <c r="T5">
-        <v>1.127483289806924</v>
+        <v>1.136704954523736</v>
       </c>
       <c r="U5">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>6.928036750265796</v>
+        <v>5.102066847279828</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2115,22 +2115,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09294391154964263</v>
+        <v>0.0930463774441047</v>
       </c>
       <c r="C6">
-        <v>21.1417725435395</v>
+        <v>20.85973069363558</v>
       </c>
       <c r="D6">
-        <v>22.1341725435395</v>
+        <v>22.10023069363558</v>
       </c>
       <c r="E6">
-        <v>-16.1076</v>
+        <v>-15.8595</v>
       </c>
       <c r="F6">
-        <v>0.9924000000000001</v>
+        <v>1.2405</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2151,45 +2151,45 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M6">
-        <v>0.05487972000000001</v>
+        <v>0.07604265</v>
       </c>
       <c r="N6">
-        <v>0.2251202799999998</v>
+        <v>0.2039573499999998</v>
       </c>
       <c r="O6">
-        <v>0.04952646159999995</v>
+        <v>0.04487061699999996</v>
       </c>
       <c r="P6">
-        <v>0.1755938183999998</v>
+        <v>0.1590867329999999</v>
       </c>
       <c r="Q6">
-        <v>2.3555938184</v>
+        <v>2.339086733</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09501932453087775</v>
+        <v>0.09542702888853127</v>
       </c>
       <c r="T6">
-        <v>1.136704954523736</v>
+        <v>1.146120759550376</v>
       </c>
       <c r="U6">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.04313400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>5.102066847279828</v>
+        <v>3.682144165149424</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2197,22 +2197,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0930463774441047</v>
+        <v>0.09345772333856676</v>
       </c>
       <c r="C7">
-        <v>20.85973069363558</v>
+        <v>20.47641362208633</v>
       </c>
       <c r="D7">
-        <v>22.10023069363558</v>
+        <v>21.96501362208633</v>
       </c>
       <c r="E7">
-        <v>-15.8595</v>
+        <v>-15.6114</v>
       </c>
       <c r="F7">
-        <v>1.2405</v>
+        <v>1.4886</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2233,45 +2233,45 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M7">
-        <v>0.07604265</v>
+        <v>0.10703034</v>
       </c>
       <c r="N7">
-        <v>0.2039573499999998</v>
+        <v>0.1729696599999998</v>
       </c>
       <c r="O7">
-        <v>0.04487061699999996</v>
+        <v>0.03805332519999996</v>
       </c>
       <c r="P7">
-        <v>0.1590867329999999</v>
+        <v>0.1349163347999998</v>
       </c>
       <c r="Q7">
-        <v>2.339086733</v>
+        <v>2.3149163348</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09542702888853127</v>
+        <v>0.09584340780698591</v>
       </c>
       <c r="T7">
-        <v>1.146120759550376</v>
+        <v>1.155736900854178</v>
       </c>
       <c r="U7">
-        <v>0.0613</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.047814</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>3.682144165149424</v>
+        <v>2.616080636574637</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2279,22 +2279,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09345772333856675</v>
+        <v>0.0936686092330288</v>
       </c>
       <c r="C8">
-        <v>20.47641362208633</v>
+        <v>20.15963106832638</v>
       </c>
       <c r="D8">
-        <v>21.96501362208634</v>
+        <v>21.89633106832638</v>
       </c>
       <c r="E8">
-        <v>-15.6114</v>
+        <v>-15.3633</v>
       </c>
       <c r="F8">
-        <v>1.4886</v>
+        <v>1.7367</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2315,45 +2315,45 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M8">
-        <v>0.10703034</v>
+        <v>0.13164186</v>
       </c>
       <c r="N8">
-        <v>0.1729696599999998</v>
+        <v>0.1483581399999998</v>
       </c>
       <c r="O8">
-        <v>0.03805332519999996</v>
+        <v>0.03263879079999996</v>
       </c>
       <c r="P8">
-        <v>0.1349163347999998</v>
+        <v>0.1157193491999998</v>
       </c>
       <c r="Q8">
-        <v>2.3149163348</v>
+        <v>2.2957193492</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09584340780698591</v>
+        <v>0.09626874111078365</v>
       </c>
       <c r="T8">
-        <v>1.155736900854178</v>
+        <v>1.165559840895696</v>
       </c>
       <c r="U8">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y8">
-        <v>2.616080636574637</v>
+        <v>2.126983012850166</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2361,22 +2361,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0936686092330288</v>
+        <v>0.09458305512749086</v>
       </c>
       <c r="C9">
-        <v>20.15963106832638</v>
+        <v>19.61861190399832</v>
       </c>
       <c r="D9">
-        <v>21.89633106832638</v>
+        <v>21.60341190399832</v>
       </c>
       <c r="E9">
-        <v>-15.3633</v>
+        <v>-15.1152</v>
       </c>
       <c r="F9">
-        <v>1.7367</v>
+        <v>1.9848</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2397,45 +2397,45 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M9">
-        <v>0.13164186</v>
+        <v>0.178632</v>
       </c>
       <c r="N9">
-        <v>0.1483581399999998</v>
+        <v>0.1013679999999998</v>
       </c>
       <c r="O9">
-        <v>0.03263879079999995</v>
+        <v>0.02230095999999995</v>
       </c>
       <c r="P9">
-        <v>0.1157193491999998</v>
+        <v>0.07906703999999984</v>
       </c>
       <c r="Q9">
-        <v>2.2957193492</v>
+        <v>2.25906704</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09626874111078366</v>
+        <v>0.09670332079075093</v>
       </c>
       <c r="T9">
-        <v>1.165559840895697</v>
+        <v>1.175596323112031</v>
       </c>
       <c r="U9">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>2.126983012850166</v>
+        <v>1.567468314747636</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2443,22 +2443,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09458305512749086</v>
+        <v>0.09927092119272514</v>
       </c>
       <c r="C10">
-        <v>19.61861190399832</v>
+        <v>17.98404607910573</v>
       </c>
       <c r="D10">
-        <v>21.60341190399832</v>
+        <v>20.21694607910574</v>
       </c>
       <c r="E10">
-        <v>-15.1152</v>
+        <v>-14.8671</v>
       </c>
       <c r="F10">
-        <v>1.9848</v>
+        <v>2.2329</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2479,45 +2479,45 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M10">
-        <v>0.178632</v>
+        <v>0.3277897200000001</v>
       </c>
       <c r="N10">
-        <v>0.1013679999999998</v>
+        <v>-0.04778972000000026</v>
       </c>
       <c r="O10">
-        <v>0.02230095999999995</v>
+        <v>-0.01051373840000006</v>
       </c>
       <c r="P10">
-        <v>0.07906703999999984</v>
+        <v>-0.0372759816000002</v>
       </c>
       <c r="Q10">
-        <v>2.25906704</v>
+        <v>2.1427240184</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09670332079075093</v>
+        <v>0.09729867143218175</v>
       </c>
       <c r="T10">
-        <v>1.175596323112031</v>
+        <v>1.18934576055847</v>
       </c>
       <c r="U10">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V10">
-        <v>0.22</v>
+        <v>0.1879253565365013</v>
       </c>
       <c r="W10">
-        <v>0.0702</v>
+        <v>0.1192125576604416</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y10">
-        <v>1.567468314747636</v>
+        <v>0.8542061660750061</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2525,22 +2525,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09927092119272514</v>
+        <v>0.1058977432858501</v>
       </c>
       <c r="C11">
-        <v>17.98404607910573</v>
+        <v>16.05436404273912</v>
       </c>
       <c r="D11">
-        <v>20.21694607910574</v>
+        <v>18.53536404273913</v>
       </c>
       <c r="E11">
-        <v>-14.8671</v>
+        <v>-14.619</v>
       </c>
       <c r="F11">
-        <v>2.2329</v>
+        <v>2.481</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2561,45 +2561,45 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M11">
-        <v>0.3277897200000001</v>
+        <v>0.4981848</v>
       </c>
       <c r="N11">
-        <v>-0.04778972000000026</v>
+        <v>-0.2181848000000002</v>
       </c>
       <c r="O11">
-        <v>-0.01051373840000006</v>
+        <v>-0.04800065600000004</v>
       </c>
       <c r="P11">
-        <v>-0.0372759816000002</v>
+        <v>-0.1701841440000001</v>
       </c>
       <c r="Q11">
-        <v>2.1427240184</v>
+        <v>2.009815856</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09729867143218175</v>
+        <v>0.0981117923293448</v>
       </c>
       <c r="T11">
-        <v>1.18934576055847</v>
+        <v>1.208124534165007</v>
       </c>
       <c r="U11">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V11">
-        <v>0.1879253565365013</v>
+        <v>0.1236488949482199</v>
       </c>
       <c r="W11">
-        <v>0.1192125576604416</v>
+        <v>0.1759713018943974</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y11">
-        <v>0.8542061660750061</v>
+        <v>0.5620404315828179</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2607,22 +2607,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1058977432858501</v>
+        <v>0.1074477432858501</v>
       </c>
       <c r="C12">
-        <v>16.05436404273912</v>
+        <v>15.45254210304296</v>
       </c>
       <c r="D12">
-        <v>18.53536404273913</v>
+        <v>18.18164210304296</v>
       </c>
       <c r="E12">
-        <v>-14.619</v>
+        <v>-14.3709</v>
       </c>
       <c r="F12">
-        <v>2.481</v>
+        <v>2.7291</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2643,37 +2643,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M12">
-        <v>0.4981848000000001</v>
+        <v>0.5480032800000001</v>
       </c>
       <c r="N12">
-        <v>-0.2181848000000003</v>
+        <v>-0.2680032800000003</v>
       </c>
       <c r="O12">
-        <v>-0.04800065600000007</v>
+        <v>-0.05896072160000006</v>
       </c>
       <c r="P12">
-        <v>-0.1701841440000002</v>
+        <v>-0.2090425584000002</v>
       </c>
       <c r="Q12">
-        <v>2.009815856</v>
+        <v>1.9709574416</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0981117923293448</v>
+        <v>0.09869956527686555</v>
       </c>
       <c r="T12">
-        <v>1.208124534165007</v>
+        <v>1.221698967133154</v>
       </c>
       <c r="U12">
         <v>0.2008</v>
       </c>
       <c r="V12">
-        <v>0.1236488949482199</v>
+        <v>0.1124080863165635</v>
       </c>
       <c r="W12">
-        <v>0.1759713018943974</v>
+        <v>0.1782284562676341</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.5620404315828178</v>
+        <v>0.5109458468934707</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2689,22 +2689,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1074477432858501</v>
+        <v>0.1132852336193464</v>
       </c>
       <c r="C13">
-        <v>15.45254210304296</v>
+        <v>13.98532387220343</v>
       </c>
       <c r="D13">
-        <v>18.18164210304296</v>
+        <v>16.96252387220343</v>
       </c>
       <c r="E13">
-        <v>-14.3709</v>
+        <v>-14.1228</v>
       </c>
       <c r="F13">
-        <v>2.7291</v>
+        <v>2.9772</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2725,45 +2725,45 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M13">
-        <v>0.5480032800000001</v>
+        <v>0.7020237600000001</v>
       </c>
       <c r="N13">
-        <v>-0.2680032800000003</v>
+        <v>-0.4220237600000003</v>
       </c>
       <c r="O13">
-        <v>-0.05896072160000006</v>
+        <v>-0.09284522720000006</v>
       </c>
       <c r="P13">
-        <v>-0.2090425584000002</v>
+        <v>-0.3291785328000003</v>
       </c>
       <c r="Q13">
-        <v>1.9709574416</v>
+        <v>1.8508214672</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09869956527686555</v>
+        <v>0.09940011753398489</v>
       </c>
       <c r="T13">
-        <v>1.221698967133154</v>
+        <v>1.237878003094339</v>
       </c>
       <c r="U13">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.1124080863165635</v>
+        <v>0.08774631787391347</v>
       </c>
       <c r="W13">
-        <v>0.1782284562676341</v>
+        <v>0.2151094182453312</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y13">
-        <v>0.5109458468934707</v>
+        <v>0.3988468994268795</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2771,22 +2771,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1132852336193464</v>
+        <v>0.1151852336193465</v>
       </c>
       <c r="C14">
-        <v>13.98532387220343</v>
+        <v>13.37493549874018</v>
       </c>
       <c r="D14">
-        <v>16.96252387220343</v>
+        <v>16.60023549874018</v>
       </c>
       <c r="E14">
-        <v>-14.1228</v>
+        <v>-13.8747</v>
       </c>
       <c r="F14">
-        <v>2.9772</v>
+        <v>3.2253</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2807,37 +2807,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M14">
-        <v>0.7020237600000001</v>
+        <v>0.7605257400000001</v>
       </c>
       <c r="N14">
-        <v>-0.4220237600000003</v>
+        <v>-0.4805257400000003</v>
       </c>
       <c r="O14">
-        <v>-0.09284522720000006</v>
+        <v>-0.1057156628000001</v>
       </c>
       <c r="P14">
-        <v>-0.3291785328000003</v>
+        <v>-0.3748100772000002</v>
       </c>
       <c r="Q14">
-        <v>1.8508214672</v>
+        <v>1.8051899228</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09940011753398489</v>
+        <v>0.1000162108389732</v>
       </c>
       <c r="T14">
-        <v>1.237878003094339</v>
+        <v>1.252106485888527</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.08774631787391347</v>
+        <v>0.08099660111438169</v>
       </c>
       <c r="W14">
-        <v>0.2151094182453312</v>
+        <v>0.2167010014572288</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.3988468994268795</v>
+        <v>0.3681663687017349</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2853,22 +2853,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1151852336193465</v>
+        <v>0.1170852336193465</v>
       </c>
       <c r="C15">
-        <v>13.37493549874018</v>
+        <v>12.77969913543271</v>
       </c>
       <c r="D15">
-        <v>16.60023549874018</v>
+        <v>16.25309913543271</v>
       </c>
       <c r="E15">
-        <v>-13.8747</v>
+        <v>-13.6266</v>
       </c>
       <c r="F15">
-        <v>3.2253</v>
+        <v>3.473400000000001</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2889,37 +2889,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M15">
-        <v>0.7605257400000001</v>
+        <v>0.8190277200000002</v>
       </c>
       <c r="N15">
-        <v>-0.4805257400000003</v>
+        <v>-0.5390277200000004</v>
       </c>
       <c r="O15">
-        <v>-0.1057156628000001</v>
+        <v>-0.1185860984000001</v>
       </c>
       <c r="P15">
-        <v>-0.3748100772000002</v>
+        <v>-0.4204416216000003</v>
       </c>
       <c r="Q15">
-        <v>1.8051899228</v>
+        <v>1.7595583784</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1000162108389732</v>
+        <v>0.1006466318952404</v>
       </c>
       <c r="T15">
-        <v>1.252106485888527</v>
+        <v>1.266665863631417</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.08099660111438169</v>
+        <v>0.07521112960621154</v>
       </c>
       <c r="W15">
-        <v>0.2167010014572288</v>
+        <v>0.2180652156388553</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.3681663687017349</v>
+        <v>0.3418687709373252</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2935,22 +2935,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1170852336193465</v>
+        <v>0.1189852336193465</v>
       </c>
       <c r="C16">
-        <v>12.77969913543271</v>
+        <v>12.19868369743581</v>
       </c>
       <c r="D16">
-        <v>16.25309913543271</v>
+        <v>15.92018369743581</v>
       </c>
       <c r="E16">
-        <v>-13.6266</v>
+        <v>-13.3785</v>
       </c>
       <c r="F16">
-        <v>3.473400000000001</v>
+        <v>3.721500000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2971,37 +2971,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M16">
-        <v>0.8190277200000002</v>
+        <v>0.8775297000000002</v>
       </c>
       <c r="N16">
-        <v>-0.5390277200000004</v>
+        <v>-0.5975297000000004</v>
       </c>
       <c r="O16">
-        <v>-0.1185860984000001</v>
+        <v>-0.1314565340000001</v>
       </c>
       <c r="P16">
-        <v>-0.4204416216000003</v>
+        <v>-0.4660731660000003</v>
       </c>
       <c r="Q16">
-        <v>1.7595583784</v>
+        <v>1.713926834</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1006466318952404</v>
+        <v>0.1012918863881255</v>
       </c>
       <c r="T16">
-        <v>1.266665863631417</v>
+        <v>1.281567814968257</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.07521112960621154</v>
+        <v>0.07019705429913078</v>
       </c>
       <c r="W16">
-        <v>0.2180652156388553</v>
+        <v>0.219247534596265</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.3418687709373252</v>
+        <v>0.3190775195415035</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1189852336193464</v>
+        <v>0.1208852336193464</v>
       </c>
       <c r="C17">
-        <v>12.19868369743581</v>
+        <v>11.63103285505843</v>
       </c>
       <c r="D17">
-        <v>15.92018369743581</v>
+        <v>15.60063285505843</v>
       </c>
       <c r="E17">
-        <v>-13.3785</v>
+        <v>-13.1304</v>
       </c>
       <c r="F17">
-        <v>3.7215</v>
+        <v>3.9696</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3053,37 +3053,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M17">
-        <v>0.8775297000000001</v>
+        <v>0.9360316800000001</v>
       </c>
       <c r="N17">
-        <v>-0.5975297000000003</v>
+        <v>-0.6560316800000003</v>
       </c>
       <c r="O17">
-        <v>-0.1314565340000001</v>
+        <v>-0.1443269696000001</v>
       </c>
       <c r="P17">
-        <v>-0.4660731660000002</v>
+        <v>-0.5117047104000003</v>
       </c>
       <c r="Q17">
-        <v>1.713926834</v>
+        <v>1.6682952896</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1012918863881255</v>
+        <v>0.1019525040832223</v>
       </c>
       <c r="T17">
-        <v>1.281567814968257</v>
+        <v>1.29682457467026</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.0701970542991308</v>
+        <v>0.06580973840543511</v>
       </c>
       <c r="W17">
-        <v>0.219247534596265</v>
+        <v>0.2202820636839984</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.3190775195415035</v>
+        <v>0.2991351745701596</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3099,22 +3099,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1208852336193464</v>
+        <v>0.1227852336193465</v>
       </c>
       <c r="C18">
-        <v>11.63103285505843</v>
+        <v>11.07595767894133</v>
       </c>
       <c r="D18">
-        <v>15.60063285505843</v>
+        <v>15.29365767894133</v>
       </c>
       <c r="E18">
-        <v>-13.1304</v>
+        <v>-12.8823</v>
       </c>
       <c r="F18">
-        <v>3.9696</v>
+        <v>4.217700000000001</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3135,37 +3135,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M18">
-        <v>0.9360316800000001</v>
+        <v>0.9945336600000002</v>
       </c>
       <c r="N18">
-        <v>-0.6560316800000003</v>
+        <v>-0.7145336600000004</v>
       </c>
       <c r="O18">
-        <v>-0.1443269696000001</v>
+        <v>-0.1571974052000001</v>
       </c>
       <c r="P18">
-        <v>-0.5117047104000003</v>
+        <v>-0.5573362548000003</v>
       </c>
       <c r="Q18">
-        <v>1.6682952896</v>
+        <v>1.6226637452</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1019525040832223</v>
+        <v>0.102629040276996</v>
       </c>
       <c r="T18">
-        <v>1.29682457467026</v>
+        <v>1.312448967136167</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.06580973840543511</v>
+        <v>0.06193857732276246</v>
       </c>
       <c r="W18">
-        <v>0.2202820636839984</v>
+        <v>0.2211948834672926</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.2991351745701596</v>
+        <v>0.2815389878307384</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3181,22 +3181,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1227852336193465</v>
+        <v>0.1246852336193465</v>
       </c>
       <c r="C19">
-        <v>11.07595767894133</v>
+        <v>10.53273013680759</v>
       </c>
       <c r="D19">
-        <v>15.29365767894133</v>
+        <v>14.99853013680759</v>
       </c>
       <c r="E19">
-        <v>-12.8823</v>
+        <v>-12.6342</v>
       </c>
       <c r="F19">
-        <v>4.217700000000001</v>
+        <v>4.465800000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3217,37 +3217,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M19">
-        <v>0.9945336600000002</v>
+        <v>1.05303564</v>
       </c>
       <c r="N19">
-        <v>-0.7145336600000004</v>
+        <v>-0.7730356400000005</v>
       </c>
       <c r="O19">
-        <v>-0.1571974052000001</v>
+        <v>-0.1700678408000001</v>
       </c>
       <c r="P19">
-        <v>-0.5573362548000003</v>
+        <v>-0.6029677992000004</v>
       </c>
       <c r="Q19">
-        <v>1.6226637452</v>
+        <v>1.5770322008</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.102629040276996</v>
+        <v>0.1033220773535448</v>
       </c>
       <c r="T19">
-        <v>1.312448967136167</v>
+        <v>1.328454442345145</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.06193857732276246</v>
+        <v>0.05849754524927565</v>
       </c>
       <c r="W19">
-        <v>0.2211948834672926</v>
+        <v>0.2220062788302208</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.2815389878307384</v>
+        <v>0.265897932951253</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3263,22 +3263,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1246852336193465</v>
+        <v>0.1265852336193465</v>
       </c>
       <c r="C20">
-        <v>10.53273013680759</v>
+        <v>10.00067732893193</v>
       </c>
       <c r="D20">
-        <v>14.99853013680759</v>
+        <v>14.71457732893193</v>
       </c>
       <c r="E20">
-        <v>-12.6342</v>
+        <v>-12.3861</v>
       </c>
       <c r="F20">
-        <v>4.465800000000001</v>
+        <v>4.713900000000001</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3299,37 +3299,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M20">
-        <v>1.05303564</v>
+        <v>1.11153762</v>
       </c>
       <c r="N20">
-        <v>-0.7730356400000005</v>
+        <v>-0.8315376200000004</v>
       </c>
       <c r="O20">
-        <v>-0.1700678408000001</v>
+        <v>-0.1829382764000001</v>
       </c>
       <c r="P20">
-        <v>-0.6029677992000004</v>
+        <v>-0.6485993436000004</v>
       </c>
       <c r="Q20">
-        <v>1.5770322008</v>
+        <v>1.5314006564</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1033220773535448</v>
+        <v>0.1040322264566749</v>
       </c>
       <c r="T20">
-        <v>1.328454442345145</v>
+        <v>1.344855114472862</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.05849754524927565</v>
+        <v>0.05541872707826114</v>
       </c>
       <c r="W20">
-        <v>0.2220062788302208</v>
+        <v>0.222732264154946</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.265897932951253</v>
+        <v>0.2519033049011871</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3345,22 +3345,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1265852336193465</v>
+        <v>0.1284852336193464</v>
       </c>
       <c r="C21">
-        <v>10.00067732893193</v>
+        <v>9.47917636624954</v>
       </c>
       <c r="D21">
-        <v>14.71457732893193</v>
+        <v>14.44117636624954</v>
       </c>
       <c r="E21">
-        <v>-12.3861</v>
+        <v>-12.138</v>
       </c>
       <c r="F21">
-        <v>4.713900000000001</v>
+        <v>4.962000000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3381,37 +3381,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M21">
-        <v>1.11153762</v>
+        <v>1.1700396</v>
       </c>
       <c r="N21">
-        <v>-0.8315376200000004</v>
+        <v>-0.8900396000000004</v>
       </c>
       <c r="O21">
-        <v>-0.1829382764000001</v>
+        <v>-0.1958087120000001</v>
       </c>
       <c r="P21">
-        <v>-0.6485993436000004</v>
+        <v>-0.6942308880000003</v>
       </c>
       <c r="Q21">
-        <v>1.5314006564</v>
+        <v>1.485769112</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1040322264566749</v>
+        <v>0.1047601292873834</v>
       </c>
       <c r="T21">
-        <v>1.344855114472862</v>
+        <v>1.361665803403773</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.05541872707826114</v>
+        <v>0.05264779072434809</v>
       </c>
       <c r="W21">
-        <v>0.222732264154946</v>
+        <v>0.2233856509471987</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2519033049011871</v>
+        <v>0.2393081396561276</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3427,22 +3427,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1284852336193464</v>
+        <v>0.1303852336193465</v>
       </c>
       <c r="C22">
-        <v>9.47917636624954</v>
+        <v>8.967649809046165</v>
       </c>
       <c r="D22">
-        <v>14.44117636624954</v>
+        <v>14.17774980904617</v>
       </c>
       <c r="E22">
-        <v>-12.138</v>
+        <v>-11.8899</v>
       </c>
       <c r="F22">
-        <v>4.962000000000001</v>
+        <v>5.210100000000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3463,37 +3463,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M22">
-        <v>1.1700396</v>
+        <v>1.22854158</v>
       </c>
       <c r="N22">
-        <v>-0.8900396000000004</v>
+        <v>-0.9485415800000003</v>
       </c>
       <c r="O22">
-        <v>-0.1958087120000001</v>
+        <v>-0.2086791476000001</v>
       </c>
       <c r="P22">
-        <v>-0.6942308880000003</v>
+        <v>-0.7398624324000003</v>
       </c>
       <c r="Q22">
-        <v>1.485769112</v>
+        <v>1.4401375676</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1047601292873834</v>
+        <v>0.1055064600378566</v>
       </c>
       <c r="T22">
-        <v>1.361665803403773</v>
+        <v>1.378902079396226</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.05264779072434809</v>
+        <v>0.05014075307080771</v>
       </c>
       <c r="W22">
-        <v>0.2233856509471987</v>
+        <v>0.2239768104259036</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2393081396561276</v>
+        <v>0.2279125139582169</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3509,22 +3509,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1303852336193465</v>
+        <v>0.1322852336193464</v>
       </c>
       <c r="C23">
-        <v>8.967649809046165</v>
+        <v>8.46556159593155</v>
       </c>
       <c r="D23">
-        <v>14.17774980904617</v>
+        <v>13.92376159593155</v>
       </c>
       <c r="E23">
-        <v>-11.8899</v>
+        <v>-11.6418</v>
       </c>
       <c r="F23">
-        <v>5.210100000000001</v>
+        <v>5.458200000000001</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3545,37 +3545,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M23">
-        <v>1.22854158</v>
+        <v>1.28704356</v>
       </c>
       <c r="N23">
-        <v>-0.9485415800000003</v>
+        <v>-1.00704356</v>
       </c>
       <c r="O23">
-        <v>-0.2086791476000001</v>
+        <v>-0.2215495832000001</v>
       </c>
       <c r="P23">
-        <v>-0.7398624324000003</v>
+        <v>-0.7854939768000002</v>
       </c>
       <c r="Q23">
-        <v>1.4401375676</v>
+        <v>1.3945060232</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1055064600378566</v>
+        <v>0.1062719274742394</v>
       </c>
       <c r="T23">
-        <v>1.378902079396226</v>
+        <v>1.396580311183357</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.05014075307080771</v>
+        <v>0.04786162793122554</v>
       </c>
       <c r="W23">
-        <v>0.2239768104259036</v>
+        <v>0.224514228133817</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2279125139582169</v>
+        <v>0.2175528542328433</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3591,22 +3591,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1322852336193464</v>
+        <v>0.1341852336193465</v>
       </c>
       <c r="C24">
-        <v>8.46556159593155</v>
+        <v>7.972413402695626</v>
       </c>
       <c r="D24">
-        <v>13.92376159593155</v>
+        <v>13.67871340269563</v>
       </c>
       <c r="E24">
-        <v>-11.6418</v>
+        <v>-11.3937</v>
       </c>
       <c r="F24">
-        <v>5.458200000000001</v>
+        <v>5.706300000000001</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3627,37 +3627,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M24">
-        <v>1.28704356</v>
+        <v>1.34554554</v>
       </c>
       <c r="N24">
-        <v>-1.00704356</v>
+        <v>-1.06554554</v>
       </c>
       <c r="O24">
-        <v>-0.2215495832000001</v>
+        <v>-0.2344200188000001</v>
       </c>
       <c r="P24">
-        <v>-0.7854939768000002</v>
+        <v>-0.8311255212000004</v>
       </c>
       <c r="Q24">
-        <v>1.3945060232</v>
+        <v>1.3488744788</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1062719274742394</v>
+        <v>0.107057277181697</v>
       </c>
       <c r="T24">
-        <v>1.396580311183357</v>
+        <v>1.414717717822102</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.04786162793122554</v>
+        <v>0.04578068758638964</v>
       </c>
       <c r="W24">
-        <v>0.224514228133817</v>
+        <v>0.2250049138671293</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2175528542328433</v>
+        <v>0.2080940344835893</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3673,22 +3673,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1341852336193465</v>
+        <v>0.1360852336193465</v>
       </c>
       <c r="C25">
-        <v>7.972413402695626</v>
+        <v>7.487741379004178</v>
       </c>
       <c r="D25">
-        <v>13.67871340269563</v>
+        <v>13.44214137900418</v>
       </c>
       <c r="E25">
-        <v>-11.3937</v>
+        <v>-11.1456</v>
       </c>
       <c r="F25">
-        <v>5.706300000000001</v>
+        <v>5.954400000000001</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3709,37 +3709,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M25">
-        <v>1.34554554</v>
+        <v>1.40404752</v>
       </c>
       <c r="N25">
-        <v>-1.06554554</v>
+        <v>-1.12404752</v>
       </c>
       <c r="O25">
-        <v>-0.2344200188000001</v>
+        <v>-0.2472904544000001</v>
       </c>
       <c r="P25">
-        <v>-0.8311255212000004</v>
+        <v>-0.8767570656000003</v>
       </c>
       <c r="Q25">
-        <v>1.3488744788</v>
+        <v>1.3032429344</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.107057277181697</v>
+        <v>0.1078632939867194</v>
       </c>
       <c r="T25">
-        <v>1.414717717822102</v>
+        <v>1.433332424635551</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.04578068758638964</v>
+        <v>0.04387315893695674</v>
       </c>
       <c r="W25">
-        <v>0.2250049138671293</v>
+        <v>0.2254547091226656</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2080940344835893</v>
+        <v>0.1994234497134397</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3755,22 +3755,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1360852336193464</v>
+        <v>0.1379852336193464</v>
       </c>
       <c r="C26">
-        <v>7.487741379004182</v>
+        <v>7.011113217968592</v>
       </c>
       <c r="D26">
-        <v>13.44214137900418</v>
+        <v>13.21361321796859</v>
       </c>
       <c r="E26">
-        <v>-11.1456</v>
+        <v>-10.8975</v>
       </c>
       <c r="F26">
-        <v>5.954400000000001</v>
+        <v>6.202500000000001</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3791,37 +3791,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M26">
-        <v>1.40404752</v>
+        <v>1.4625495</v>
       </c>
       <c r="N26">
-        <v>-1.12404752</v>
+        <v>-1.1825495</v>
       </c>
       <c r="O26">
-        <v>-0.2472904544000001</v>
+        <v>-0.2601608900000001</v>
       </c>
       <c r="P26">
-        <v>-0.8767570656000003</v>
+        <v>-0.9223886100000003</v>
       </c>
       <c r="Q26">
-        <v>1.3032429344</v>
+        <v>1.25761139</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1078632939867193</v>
+        <v>0.1086908045732089</v>
       </c>
       <c r="T26">
-        <v>1.433332424635551</v>
+        <v>1.452443523630691</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.04387315893695674</v>
+        <v>0.04211823257947847</v>
       </c>
       <c r="W26">
-        <v>0.2254547091226656</v>
+        <v>0.225868520757759</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.1994234497134397</v>
+        <v>0.1914465117249021</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3837,22 +3837,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1379852336193464</v>
+        <v>0.1398852336193465</v>
       </c>
       <c r="C27">
-        <v>7.011113217968592</v>
+        <v>6.542125519637971</v>
       </c>
       <c r="D27">
-        <v>13.21361321796859</v>
+        <v>12.99272551963797</v>
       </c>
       <c r="E27">
-        <v>-10.8975</v>
+        <v>-10.6494</v>
       </c>
       <c r="F27">
-        <v>6.202500000000001</v>
+        <v>6.450600000000001</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3873,37 +3873,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M27">
-        <v>1.4625495</v>
+        <v>1.52105148</v>
       </c>
       <c r="N27">
-        <v>-1.1825495</v>
+        <v>-1.24105148</v>
       </c>
       <c r="O27">
-        <v>-0.2601608900000001</v>
+        <v>-0.2730313256000001</v>
       </c>
       <c r="P27">
-        <v>-0.9223886100000003</v>
+        <v>-0.9680201544000002</v>
       </c>
       <c r="Q27">
-        <v>1.25761139</v>
+        <v>1.2119798456</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1086908045732089</v>
+        <v>0.1095406803106847</v>
       </c>
       <c r="T27">
-        <v>1.452443523630691</v>
+        <v>1.47207113881489</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.04211823257947847</v>
+        <v>0.04049830055719084</v>
       </c>
       <c r="W27">
-        <v>0.225868520757759</v>
+        <v>0.2262505007286144</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.1914465117249021</v>
+        <v>0.1840831843508675</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3919,22 +3919,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1398852336193465</v>
+        <v>0.1417852336193464</v>
       </c>
       <c r="C28">
-        <v>6.542125519637971</v>
+        <v>6.080401414585256</v>
       </c>
       <c r="D28">
-        <v>12.99272551963797</v>
+        <v>12.77910141458526</v>
       </c>
       <c r="E28">
-        <v>-10.6494</v>
+        <v>-10.4013</v>
       </c>
       <c r="F28">
-        <v>6.450600000000001</v>
+        <v>6.698700000000001</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3955,37 +3955,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M28">
-        <v>1.52105148</v>
+        <v>1.57955346</v>
       </c>
       <c r="N28">
-        <v>-1.24105148</v>
+        <v>-1.29955346</v>
       </c>
       <c r="O28">
-        <v>-0.2730313256000001</v>
+        <v>-0.2859017612000001</v>
       </c>
       <c r="P28">
-        <v>-0.9680201544000002</v>
+        <v>-1.0136516988</v>
       </c>
       <c r="Q28">
-        <v>1.2119798456</v>
+        <v>1.1663483012</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1095406803106847</v>
+        <v>0.1104138403149407</v>
       </c>
       <c r="T28">
-        <v>1.47207113881489</v>
+        <v>1.492236496880847</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.04049830055719084</v>
+        <v>0.0389983634995171</v>
       </c>
       <c r="W28">
-        <v>0.2262505007286144</v>
+        <v>0.2266041858868139</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.1840831843508675</v>
+        <v>0.1772652886341687</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4001,22 +4001,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1417852336193464</v>
+        <v>0.1436852336193465</v>
       </c>
       <c r="C29">
-        <v>6.080401414585256</v>
+        <v>5.625588418136573</v>
       </c>
       <c r="D29">
-        <v>12.77910141458526</v>
+        <v>12.57238841813657</v>
       </c>
       <c r="E29">
-        <v>-10.4013</v>
+        <v>-10.1532</v>
       </c>
       <c r="F29">
-        <v>6.698700000000001</v>
+        <v>6.946800000000001</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -4037,37 +4037,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M29">
-        <v>1.57955346</v>
+        <v>1.63805544</v>
       </c>
       <c r="N29">
-        <v>-1.29955346</v>
+        <v>-1.358055440000001</v>
       </c>
       <c r="O29">
-        <v>-0.2859017612000001</v>
+        <v>-0.2987721968000002</v>
       </c>
       <c r="P29">
-        <v>-1.0136516988</v>
+        <v>-1.059283243200001</v>
       </c>
       <c r="Q29">
-        <v>1.1663483012</v>
+        <v>1.1207167568</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1104138403149407</v>
+        <v>0.1113112547637593</v>
       </c>
       <c r="T29">
-        <v>1.492236496880847</v>
+        <v>1.51296200378197</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.0389983634995171</v>
+        <v>0.03760556480310577</v>
       </c>
       <c r="W29">
-        <v>0.2266041858868139</v>
+        <v>0.2269326078194277</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.1772652886341687</v>
+        <v>0.1709343854686626</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1436852336193465</v>
+        <v>0.1455852336193464</v>
       </c>
       <c r="C30">
-        <v>5.625588418136573</v>
+        <v>5.177356489543677</v>
       </c>
       <c r="D30">
-        <v>12.57238841813657</v>
+        <v>12.37225648954368</v>
       </c>
       <c r="E30">
-        <v>-10.1532</v>
+        <v>-9.905100000000001</v>
       </c>
       <c r="F30">
-        <v>6.946800000000001</v>
+        <v>7.194900000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -4119,37 +4119,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M30">
-        <v>1.63805544</v>
+        <v>1.69655742</v>
       </c>
       <c r="N30">
-        <v>-1.358055440000001</v>
+        <v>-1.416557420000001</v>
       </c>
       <c r="O30">
-        <v>-0.2987721968000002</v>
+        <v>-0.3116426324000001</v>
       </c>
       <c r="P30">
-        <v>-1.059283243200001</v>
+        <v>-1.104914787600001</v>
       </c>
       <c r="Q30">
-        <v>1.1207167568</v>
+        <v>1.0750852124</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1113112547637593</v>
+        <v>0.1122339484928263</v>
       </c>
       <c r="T30">
-        <v>1.51296200378197</v>
+        <v>1.5342713277789</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.03760556480310577</v>
+        <v>0.03630882118920557</v>
       </c>
       <c r="W30">
-        <v>0.2269326078194277</v>
+        <v>0.2272383799635853</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1709343854686626</v>
+        <v>0.1650400963145708</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4165,22 +4165,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1455852336193464</v>
+        <v>0.1474852336193464</v>
       </c>
       <c r="C31">
-        <v>5.177356489543678</v>
+        <v>4.73539627362064</v>
       </c>
       <c r="D31">
-        <v>12.37225648954368</v>
+        <v>12.17839627362064</v>
       </c>
       <c r="E31">
-        <v>-9.905100000000001</v>
+        <v>-9.657</v>
       </c>
       <c r="F31">
-        <v>7.194900000000001</v>
+        <v>7.443000000000001</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4201,37 +4201,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M31">
-        <v>1.69655742</v>
+        <v>1.7550594</v>
       </c>
       <c r="N31">
-        <v>-1.41655742</v>
+        <v>-1.4750594</v>
       </c>
       <c r="O31">
-        <v>-0.3116426324000001</v>
+        <v>-0.3245130680000001</v>
       </c>
       <c r="P31">
-        <v>-1.1049147876</v>
+        <v>-1.150546332</v>
       </c>
       <c r="Q31">
-        <v>1.0750852124</v>
+        <v>1.029453668</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1122339484928263</v>
+        <v>0.1131830048998667</v>
       </c>
       <c r="T31">
-        <v>1.5342713277789</v>
+        <v>1.556189489604312</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.03630882118920558</v>
+        <v>0.0350985271495654</v>
       </c>
       <c r="W31">
-        <v>0.2272383799635853</v>
+        <v>0.2275237672981325</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1650400963145708</v>
+        <v>0.1595387597707518</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4247,22 +4247,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1474852336193464</v>
+        <v>0.1493852336193464</v>
       </c>
       <c r="C32">
-        <v>4.73539627362064</v>
+        <v>4.29941750514053</v>
       </c>
       <c r="D32">
-        <v>12.17839627362064</v>
+        <v>11.99051750514053</v>
       </c>
       <c r="E32">
-        <v>-9.657</v>
+        <v>-9.408900000000001</v>
       </c>
       <c r="F32">
-        <v>7.443000000000001</v>
+        <v>7.6911</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4283,37 +4283,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M32">
-        <v>1.7550594</v>
+        <v>1.81356138</v>
       </c>
       <c r="N32">
-        <v>-1.4750594</v>
+        <v>-1.53356138</v>
       </c>
       <c r="O32">
-        <v>-0.3245130680000001</v>
+        <v>-0.3373835036000001</v>
       </c>
       <c r="P32">
-        <v>-1.150546332</v>
+        <v>-1.1961778764</v>
       </c>
       <c r="Q32">
-        <v>1.029453668</v>
+        <v>0.9838221236</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1131830048998667</v>
+        <v>0.1141595701882706</v>
       </c>
       <c r="T32">
-        <v>1.556189489604312</v>
+        <v>1.578742960468143</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.0350985271495654</v>
+        <v>0.03396631659635361</v>
       </c>
       <c r="W32">
-        <v>0.2275237672981325</v>
+        <v>0.2277907425465798</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1595387597707518</v>
+        <v>0.1543923481652437</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4329,22 +4329,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1493852336193464</v>
+        <v>0.1512852336193464</v>
       </c>
       <c r="C33">
-        <v>4.29941750514053</v>
+        <v>3.869147558682482</v>
       </c>
       <c r="D33">
-        <v>11.99051750514053</v>
+        <v>11.80834755868248</v>
       </c>
       <c r="E33">
-        <v>-9.408900000000001</v>
+        <v>-9.160800000000002</v>
       </c>
       <c r="F33">
-        <v>7.6911</v>
+        <v>7.9392</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4365,37 +4365,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M33">
-        <v>1.81356138</v>
+        <v>1.87206336</v>
       </c>
       <c r="N33">
-        <v>-1.53356138</v>
+        <v>-1.59206336</v>
       </c>
       <c r="O33">
-        <v>-0.3373835036000001</v>
+        <v>-0.3502539392000001</v>
       </c>
       <c r="P33">
-        <v>-1.1961778764</v>
+        <v>-1.2418094208</v>
       </c>
       <c r="Q33">
-        <v>0.9838221236</v>
+        <v>0.9381905791999998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1141595701882706</v>
+        <v>0.1151648579851569</v>
       </c>
       <c r="T33">
-        <v>1.578742960468143</v>
+        <v>1.601959768710322</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03396631659635361</v>
+        <v>0.03290486920271755</v>
       </c>
       <c r="W33">
-        <v>0.2277907425465798</v>
+        <v>0.2280410318419992</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.1543923481652437</v>
+        <v>0.1495675872850798</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4411,22 +4411,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1512852336193464</v>
+        <v>0.1531852336193464</v>
       </c>
       <c r="C34">
-        <v>3.869147558682482</v>
+        <v>3.444330128692055</v>
       </c>
       <c r="D34">
-        <v>11.80834755868248</v>
+        <v>11.63163012869206</v>
       </c>
       <c r="E34">
-        <v>-9.160800000000002</v>
+        <v>-8.912700000000001</v>
       </c>
       <c r="F34">
-        <v>7.9392</v>
+        <v>8.1873</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4447,37 +4447,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M34">
-        <v>1.87206336</v>
+        <v>1.93056534</v>
       </c>
       <c r="N34">
-        <v>-1.59206336</v>
+        <v>-1.65056534</v>
       </c>
       <c r="O34">
-        <v>-0.3502539392000001</v>
+        <v>-0.3631243748000001</v>
       </c>
       <c r="P34">
-        <v>-1.2418094208</v>
+        <v>-1.2874409652</v>
       </c>
       <c r="Q34">
-        <v>0.9381905791999998</v>
+        <v>0.8925590347999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1151648579851569</v>
+        <v>0.1162001543729951</v>
       </c>
       <c r="T34">
-        <v>1.601959768710322</v>
+        <v>1.625869616004505</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.03290486920271755</v>
+        <v>0.03190775195415036</v>
       </c>
       <c r="W34">
-        <v>0.2280410318419992</v>
+        <v>0.2282761520892113</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.1495675872850798</v>
+        <v>0.145035236155229</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4493,22 +4493,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1531852336193464</v>
+        <v>0.1550852336193465</v>
       </c>
       <c r="C35">
-        <v>3.444330128692055</v>
+        <v>3.024724026315104</v>
       </c>
       <c r="D35">
-        <v>11.63163012869206</v>
+        <v>11.46012402631511</v>
       </c>
       <c r="E35">
-        <v>-8.912700000000001</v>
+        <v>-8.6646</v>
       </c>
       <c r="F35">
-        <v>8.1873</v>
+        <v>8.435400000000001</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4529,37 +4529,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M35">
-        <v>1.93056534</v>
+        <v>1.98906732</v>
       </c>
       <c r="N35">
-        <v>-1.65056534</v>
+        <v>-1.709067320000001</v>
       </c>
       <c r="O35">
-        <v>-0.3631243748000001</v>
+        <v>-0.3759948104000002</v>
       </c>
       <c r="P35">
-        <v>-1.2874409652</v>
+        <v>-1.3330725096</v>
       </c>
       <c r="Q35">
-        <v>0.8925590347999999</v>
+        <v>0.8469274903999997</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1162001543729951</v>
+        <v>0.1172668233786465</v>
       </c>
       <c r="T35">
-        <v>1.625869616004505</v>
+        <v>1.650504004125786</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.03190775195415036</v>
+        <v>0.03096928866138123</v>
       </c>
       <c r="W35">
-        <v>0.2282761520892113</v>
+        <v>0.2284974417336463</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.145035236155229</v>
+        <v>0.1407694939153692</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4575,22 +4575,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1550852336193465</v>
+        <v>0.1569852336193464</v>
       </c>
       <c r="C36">
-        <v>3.024724026315104</v>
+        <v>2.610102081127687</v>
       </c>
       <c r="D36">
-        <v>11.46012402631511</v>
+        <v>11.29360208112769</v>
       </c>
       <c r="E36">
-        <v>-8.6646</v>
+        <v>-8.416499999999999</v>
       </c>
       <c r="F36">
-        <v>8.435400000000001</v>
+        <v>8.683500000000002</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4611,37 +4611,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M36">
-        <v>1.98906732</v>
+        <v>2.047569300000001</v>
       </c>
       <c r="N36">
-        <v>-1.709067320000001</v>
+        <v>-1.767569300000001</v>
       </c>
       <c r="O36">
-        <v>-0.3759948104000002</v>
+        <v>-0.3888652460000002</v>
       </c>
       <c r="P36">
-        <v>-1.3330725096</v>
+        <v>-1.378704054000001</v>
       </c>
       <c r="Q36">
-        <v>0.8469274903999997</v>
+        <v>0.8012959459999995</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1172668233786465</v>
+        <v>0.1183663129690872</v>
       </c>
       <c r="T36">
-        <v>1.650504004125786</v>
+        <v>1.675896373420029</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.03096928866138123</v>
+        <v>0.03008445184248462</v>
       </c>
       <c r="W36">
-        <v>0.2284974417336463</v>
+        <v>0.2287060862555421</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1407694939153692</v>
+        <v>0.1367475083749301</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4657,22 +4657,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1569852336193464</v>
+        <v>0.1588852336193464</v>
       </c>
       <c r="C37">
-        <v>2.610102081127687</v>
+        <v>2.200250137245371</v>
       </c>
       <c r="D37">
-        <v>11.29360208112769</v>
+        <v>11.13185013724537</v>
       </c>
       <c r="E37">
-        <v>-8.416499999999999</v>
+        <v>-8.1684</v>
       </c>
       <c r="F37">
-        <v>8.683500000000002</v>
+        <v>8.931600000000001</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4693,37 +4693,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M37">
-        <v>2.047569300000001</v>
+        <v>2.106071280000001</v>
       </c>
       <c r="N37">
-        <v>-1.767569300000001</v>
+        <v>-1.826071280000001</v>
       </c>
       <c r="O37">
-        <v>-0.3888652460000002</v>
+        <v>-0.4017356816000002</v>
       </c>
       <c r="P37">
-        <v>-1.378704054000001</v>
+        <v>-1.424335598400001</v>
       </c>
       <c r="Q37">
-        <v>0.8012959459999995</v>
+        <v>0.7556644015999996</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1183663129690872</v>
+        <v>0.1195001616092292</v>
       </c>
       <c r="T37">
-        <v>1.675896373420029</v>
+        <v>1.702082254254717</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03008445184248462</v>
+        <v>0.02924877262463783</v>
       </c>
       <c r="W37">
-        <v>0.2287060862555421</v>
+        <v>0.2289031394151104</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1367475083749301</v>
+        <v>0.1329489664756265</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4739,22 +4739,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1588852336193464</v>
+        <v>0.1607852336193464</v>
       </c>
       <c r="C38">
-        <v>2.200250137245373</v>
+        <v>1.794966134483442</v>
       </c>
       <c r="D38">
-        <v>11.13185013724537</v>
+        <v>10.97466613448344</v>
       </c>
       <c r="E38">
-        <v>-8.1684</v>
+        <v>-7.920300000000001</v>
       </c>
       <c r="F38">
-        <v>8.931600000000001</v>
+        <v>9.1797</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4775,37 +4775,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M38">
-        <v>2.106071280000001</v>
+        <v>2.16457326</v>
       </c>
       <c r="N38">
-        <v>-1.826071280000001</v>
+        <v>-1.88457326</v>
       </c>
       <c r="O38">
-        <v>-0.4017356816000002</v>
+        <v>-0.4146061172000001</v>
       </c>
       <c r="P38">
-        <v>-1.424335598400001</v>
+        <v>-1.4699671428</v>
       </c>
       <c r="Q38">
-        <v>0.7556644015999996</v>
+        <v>0.7100328571999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1195001616092292</v>
+        <v>0.1206700054442963</v>
       </c>
       <c r="T38">
-        <v>1.702082254254716</v>
+        <v>1.72909943289368</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.02924877262463783</v>
+        <v>0.02845826525640437</v>
       </c>
       <c r="W38">
-        <v>0.2289031394151104</v>
+        <v>0.2290895410525399</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1329489664756265</v>
+        <v>0.1293557511654745</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4821,22 +4821,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1607852336193464</v>
+        <v>0.1626852336193464</v>
       </c>
       <c r="C39">
-        <v>1.794966134483442</v>
+        <v>1.394059266278433</v>
       </c>
       <c r="D39">
-        <v>10.97466613448344</v>
+        <v>10.82185926627843</v>
       </c>
       <c r="E39">
-        <v>-7.920300000000001</v>
+        <v>-7.6722</v>
       </c>
       <c r="F39">
-        <v>9.1797</v>
+        <v>9.427800000000001</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4857,37 +4857,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M39">
-        <v>2.16457326</v>
+        <v>2.22307524</v>
       </c>
       <c r="N39">
-        <v>-1.88457326</v>
+        <v>-1.943075240000001</v>
       </c>
       <c r="O39">
-        <v>-0.4146061172000001</v>
+        <v>-0.4274765528000001</v>
       </c>
       <c r="P39">
-        <v>-1.4699671428</v>
+        <v>-1.5155986872</v>
       </c>
       <c r="Q39">
-        <v>0.7100328571999999</v>
+        <v>0.6644013127999997</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1206700054442963</v>
+        <v>0.1218775861772689</v>
       </c>
       <c r="T39">
-        <v>1.72909943289368</v>
+        <v>1.756988133424224</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02845826525640437</v>
+        <v>0.02770936353913057</v>
       </c>
       <c r="W39">
-        <v>0.2290895410525399</v>
+        <v>0.229266132077473</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1293557511654745</v>
+        <v>0.1259516524505935</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4903,22 +4903,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1626852336193464</v>
+        <v>0.1645852336193465</v>
       </c>
       <c r="C40">
-        <v>1.394059266278433</v>
+        <v>0.9973492069922099</v>
       </c>
       <c r="D40">
-        <v>10.82185926627843</v>
+        <v>10.67324920699221</v>
       </c>
       <c r="E40">
-        <v>-7.6722</v>
+        <v>-7.424100000000001</v>
       </c>
       <c r="F40">
-        <v>9.427800000000001</v>
+        <v>9.6759</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4939,37 +4939,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M40">
-        <v>2.22307524</v>
+        <v>2.28157722</v>
       </c>
       <c r="N40">
-        <v>-1.943075240000001</v>
+        <v>-2.001577220000001</v>
       </c>
       <c r="O40">
-        <v>-0.4274765528000001</v>
+        <v>-0.4403469884000001</v>
       </c>
       <c r="P40">
-        <v>-1.5155986872</v>
+        <v>-1.5612302316</v>
       </c>
       <c r="Q40">
-        <v>0.6644013127999997</v>
+        <v>0.6187697683999998</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1218775861772689</v>
+        <v>0.1231247597211585</v>
       </c>
       <c r="T40">
-        <v>1.756988133424224</v>
+        <v>1.785791217578719</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02770936353913057</v>
+        <v>0.02699886703812723</v>
       </c>
       <c r="W40">
-        <v>0.229266132077473</v>
+        <v>0.2294336671524096</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1259516524505935</v>
+        <v>0.1227221229005783</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4985,22 +4985,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1645852336193465</v>
+        <v>0.1664852336193465</v>
       </c>
       <c r="C41">
-        <v>0.9973492069922099</v>
+        <v>0.6046654020193909</v>
       </c>
       <c r="D41">
-        <v>10.67324920699221</v>
+        <v>10.52866540201939</v>
       </c>
       <c r="E41">
-        <v>-7.424100000000001</v>
+        <v>-7.176</v>
       </c>
       <c r="F41">
-        <v>9.6759</v>
+        <v>9.924000000000001</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -5021,37 +5021,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M41">
-        <v>2.28157722</v>
+        <v>2.3400792</v>
       </c>
       <c r="N41">
-        <v>-2.001577220000001</v>
+        <v>-2.060079200000001</v>
       </c>
       <c r="O41">
-        <v>-0.4403469884000001</v>
+        <v>-0.4532174240000001</v>
       </c>
       <c r="P41">
-        <v>-1.5612302316</v>
+        <v>-1.606861776</v>
       </c>
       <c r="Q41">
-        <v>0.6187697683999998</v>
+        <v>0.5731382239999998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1231247597211585</v>
+        <v>0.1244135057165112</v>
       </c>
       <c r="T41">
-        <v>1.785791217578719</v>
+        <v>1.815554404538364</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02699886703812723</v>
+        <v>0.02632389536217404</v>
       </c>
       <c r="W41">
-        <v>0.2294336671524096</v>
+        <v>0.2295928254735994</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1227221229005783</v>
+        <v>0.1196540698280638</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5067,22 +5067,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1664852336193465</v>
+        <v>0.1683852336193465</v>
       </c>
       <c r="C42">
-        <v>0.6046654020193909</v>
+        <v>0.2158464148224226</v>
       </c>
       <c r="D42">
-        <v>10.52866540201939</v>
+        <v>10.38794641482242</v>
       </c>
       <c r="E42">
-        <v>-7.176</v>
+        <v>-6.927899999999999</v>
       </c>
       <c r="F42">
-        <v>9.924000000000001</v>
+        <v>10.1721</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -5103,37 +5103,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M42">
-        <v>2.3400792</v>
+        <v>2.398581180000001</v>
       </c>
       <c r="N42">
-        <v>-2.060079200000001</v>
+        <v>-2.118581180000001</v>
       </c>
       <c r="O42">
-        <v>-0.4532174240000001</v>
+        <v>-0.4660878596000002</v>
       </c>
       <c r="P42">
-        <v>-1.606861776</v>
+        <v>-1.652493320400001</v>
       </c>
       <c r="Q42">
-        <v>0.5731382239999998</v>
+        <v>0.5275066795999994</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1244135057165112</v>
+        <v>0.125745938016791</v>
       </c>
       <c r="T42">
-        <v>1.815554404538364</v>
+        <v>1.846326513089862</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02632389536217404</v>
+        <v>0.02568184913382833</v>
       </c>
       <c r="W42">
-        <v>0.2295928254735994</v>
+        <v>0.2297442199742433</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1196540698280638</v>
+        <v>0.1167356778810379</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1683852336193465</v>
+        <v>0.1702852336193464</v>
       </c>
       <c r="C43">
-        <v>0.2158464148224226</v>
+        <v>-0.1692606743614231</v>
       </c>
       <c r="D43">
-        <v>10.38794641482242</v>
+        <v>10.25093932563858</v>
       </c>
       <c r="E43">
-        <v>-6.927899999999999</v>
+        <v>-6.6798</v>
       </c>
       <c r="F43">
-        <v>10.1721</v>
+        <v>10.4202</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -5185,37 +5185,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M43">
-        <v>2.398581180000001</v>
+        <v>2.45708316</v>
       </c>
       <c r="N43">
-        <v>-2.118581180000001</v>
+        <v>-2.17708316</v>
       </c>
       <c r="O43">
-        <v>-0.4660878596000002</v>
+        <v>-0.4789582952000001</v>
       </c>
       <c r="P43">
-        <v>-1.652493320400001</v>
+        <v>-1.6981248648</v>
       </c>
       <c r="Q43">
-        <v>0.5275066795999994</v>
+        <v>0.4818751351999997</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.125745938016791</v>
+        <v>0.1271243162584598</v>
       </c>
       <c r="T43">
-        <v>1.846326513089862</v>
+        <v>1.878159728832791</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02568184913382833</v>
+        <v>0.02507037653540386</v>
       </c>
       <c r="W43">
-        <v>0.2297442199742433</v>
+        <v>0.2298884052129518</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1167356778810379</v>
+        <v>0.1139562569791084</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5231,22 +5231,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1702852336193464</v>
+        <v>0.1721852336193465</v>
       </c>
       <c r="C44">
-        <v>-0.1692606743614231</v>
+        <v>-0.5508008228496291</v>
       </c>
       <c r="D44">
-        <v>10.25093932563858</v>
+        <v>10.11749917715037</v>
       </c>
       <c r="E44">
-        <v>-6.6798</v>
+        <v>-6.431700000000001</v>
       </c>
       <c r="F44">
-        <v>10.4202</v>
+        <v>10.6683</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -5267,37 +5267,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M44">
-        <v>2.45708316</v>
+        <v>2.51558514</v>
       </c>
       <c r="N44">
-        <v>-2.17708316</v>
+        <v>-2.23558514</v>
       </c>
       <c r="O44">
-        <v>-0.4789582952000001</v>
+        <v>-0.4918287308000001</v>
       </c>
       <c r="P44">
-        <v>-1.6981248648</v>
+        <v>-1.7437564092</v>
       </c>
       <c r="Q44">
-        <v>0.4818751351999997</v>
+        <v>0.4362435907999997</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1271243162584598</v>
+        <v>0.1285510586489591</v>
       </c>
       <c r="T44">
-        <v>1.878159728832791</v>
+        <v>1.911109899514068</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02507037653540386</v>
+        <v>0.0244873445229526</v>
       </c>
       <c r="W44">
-        <v>0.2298884052129518</v>
+        <v>0.2300258841614878</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1139562569791084</v>
+        <v>0.1113061114679663</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5313,22 +5313,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1721852336193465</v>
+        <v>0.1740852336193464</v>
       </c>
       <c r="C45">
-        <v>-0.5508008228496291</v>
+        <v>-0.9289115371048222</v>
       </c>
       <c r="D45">
-        <v>10.11749917715037</v>
+        <v>9.987488462895179</v>
       </c>
       <c r="E45">
-        <v>-6.431700000000001</v>
+        <v>-6.1836</v>
       </c>
       <c r="F45">
-        <v>10.6683</v>
+        <v>10.9164</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5349,37 +5349,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M45">
-        <v>2.51558514</v>
+        <v>2.57408712</v>
       </c>
       <c r="N45">
-        <v>-2.23558514</v>
+        <v>-2.29408712</v>
       </c>
       <c r="O45">
-        <v>-0.4918287308000001</v>
+        <v>-0.5046991664000001</v>
       </c>
       <c r="P45">
-        <v>-1.7437564092</v>
+        <v>-1.7893879536</v>
       </c>
       <c r="Q45">
-        <v>0.4362435907999997</v>
+        <v>0.3906120463999998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1285510586489591</v>
+        <v>0.1300287561248334</v>
       </c>
       <c r="T45">
-        <v>1.911109899514068</v>
+        <v>1.94523686200539</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.0244873445229526</v>
+        <v>0.02393081396561277</v>
       </c>
       <c r="W45">
-        <v>0.2300258841614878</v>
+        <v>0.2301571140669085</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1113061114679663</v>
+        <v>0.1087764271164217</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5395,22 +5395,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1740852336193464</v>
+        <v>0.1759852336193465</v>
       </c>
       <c r="C46">
-        <v>-0.9289115371048222</v>
+        <v>-1.303723345381835</v>
       </c>
       <c r="D46">
-        <v>9.987488462895179</v>
+        <v>9.860776654618167</v>
       </c>
       <c r="E46">
-        <v>-6.1836</v>
+        <v>-5.935499999999999</v>
       </c>
       <c r="F46">
-        <v>10.9164</v>
+        <v>11.1645</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5431,37 +5431,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M46">
-        <v>2.57408712</v>
+        <v>2.632589100000001</v>
       </c>
       <c r="N46">
-        <v>-2.29408712</v>
+        <v>-2.352589100000001</v>
       </c>
       <c r="O46">
-        <v>-0.5046991664000001</v>
+        <v>-0.5175696020000001</v>
       </c>
       <c r="P46">
-        <v>-1.7893879536</v>
+        <v>-1.835019498000001</v>
       </c>
       <c r="Q46">
-        <v>0.3906120463999998</v>
+        <v>0.3449805019999994</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1300287561248334</v>
+        <v>0.1315601880543758</v>
       </c>
       <c r="T46">
-        <v>1.94523686200539</v>
+        <v>1.980604804950943</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02393081396561277</v>
+        <v>0.02339901809971026</v>
       </c>
       <c r="W46">
-        <v>0.2301571140669085</v>
+        <v>0.2302825115320883</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1087764271164217</v>
+        <v>0.1063591731805011</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5477,22 +5477,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1759852336193465</v>
+        <v>0.1778852336193465</v>
       </c>
       <c r="C47">
-        <v>-1.303723345381835</v>
+        <v>-1.675360234846407</v>
       </c>
       <c r="D47">
-        <v>9.860776654618167</v>
+        <v>9.737239765153594</v>
       </c>
       <c r="E47">
-        <v>-5.935499999999999</v>
+        <v>-5.6874</v>
       </c>
       <c r="F47">
-        <v>11.1645</v>
+        <v>11.4126</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5513,37 +5513,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M47">
-        <v>2.632589100000001</v>
+        <v>2.691091080000001</v>
       </c>
       <c r="N47">
-        <v>-2.352589100000001</v>
+        <v>-2.411091080000001</v>
       </c>
       <c r="O47">
-        <v>-0.5175696020000001</v>
+        <v>-0.5304400376000001</v>
       </c>
       <c r="P47">
-        <v>-1.835019498000001</v>
+        <v>-1.880651042400001</v>
       </c>
       <c r="Q47">
-        <v>0.3449805019999994</v>
+        <v>0.2993489575999995</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1315601880543758</v>
+        <v>0.1331483396850124</v>
       </c>
       <c r="T47">
-        <v>1.980604804950943</v>
+        <v>2.017282671709294</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02339901809971026</v>
+        <v>0.02289034379319482</v>
       </c>
       <c r="W47">
-        <v>0.2302825115320883</v>
+        <v>0.2304024569335647</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1063591731805011</v>
+        <v>0.1040470172417947</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5559,22 +5559,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1778852336193465</v>
+        <v>0.1797852336193465</v>
       </c>
       <c r="C48">
-        <v>-1.675360234846407</v>
+        <v>-2.043940056242919</v>
       </c>
       <c r="D48">
-        <v>9.737239765153594</v>
+        <v>9.616759943757083</v>
       </c>
       <c r="E48">
-        <v>-5.6874</v>
+        <v>-5.439299999999999</v>
       </c>
       <c r="F48">
-        <v>11.4126</v>
+        <v>11.6607</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5595,37 +5595,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M48">
-        <v>2.691091080000001</v>
+        <v>2.74959306</v>
       </c>
       <c r="N48">
-        <v>-2.411091080000001</v>
+        <v>-2.469593060000001</v>
       </c>
       <c r="O48">
-        <v>-0.5304400376000001</v>
+        <v>-0.5433104732000001</v>
       </c>
       <c r="P48">
-        <v>-1.880651042400001</v>
+        <v>-1.926282586800001</v>
       </c>
       <c r="Q48">
-        <v>0.2993489575999995</v>
+        <v>0.2537174131999995</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1331483396850124</v>
+        <v>0.1347964215658617</v>
       </c>
       <c r="T48">
-        <v>2.017282671709294</v>
+        <v>2.055344608911356</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02289034379319482</v>
+        <v>0.02240331520185025</v>
       </c>
       <c r="W48">
-        <v>0.2304024569335647</v>
+        <v>0.2305172982754037</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1040470172417947</v>
+        <v>0.1018332509175012</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5641,22 +5641,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1797852336193465</v>
+        <v>0.1816852336193465</v>
       </c>
       <c r="C49">
-        <v>-2.043940056242919</v>
+        <v>-2.409574898887234</v>
       </c>
       <c r="D49">
-        <v>9.616759943757083</v>
+        <v>9.499225101112767</v>
       </c>
       <c r="E49">
-        <v>-5.439299999999999</v>
+        <v>-5.1912</v>
       </c>
       <c r="F49">
-        <v>11.6607</v>
+        <v>11.9088</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5677,37 +5677,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M49">
-        <v>2.74959306</v>
+        <v>2.80809504</v>
       </c>
       <c r="N49">
-        <v>-2.469593060000001</v>
+        <v>-2.528095040000001</v>
       </c>
       <c r="O49">
-        <v>-0.5433104732000001</v>
+        <v>-0.5561809088000002</v>
       </c>
       <c r="P49">
-        <v>-1.926282586800001</v>
+        <v>-1.971914131200001</v>
       </c>
       <c r="Q49">
-        <v>0.2537174131999995</v>
+        <v>0.2080858687999996</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1347964215658617</v>
+        <v>0.1365078912113591</v>
       </c>
       <c r="T49">
-        <v>2.055344608911356</v>
+        <v>2.094870466775036</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02240331520185025</v>
+        <v>0.02193657946847837</v>
       </c>
       <c r="W49">
-        <v>0.2305172982754037</v>
+        <v>0.2306273545613328</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1018332509175012</v>
+        <v>0.09971172485671986</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5723,22 +5723,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1816852336193465</v>
+        <v>0.1835852336193464</v>
       </c>
       <c r="C50">
-        <v>-2.409574898887234</v>
+        <v>-2.772371438492948</v>
       </c>
       <c r="D50">
-        <v>9.499225101112767</v>
+        <v>9.384528561507052</v>
       </c>
       <c r="E50">
-        <v>-5.1912</v>
+        <v>-4.943100000000001</v>
       </c>
       <c r="F50">
-        <v>11.9088</v>
+        <v>12.1569</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5759,37 +5759,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M50">
-        <v>2.80809504</v>
+        <v>2.86659702</v>
       </c>
       <c r="N50">
-        <v>-2.528095040000001</v>
+        <v>-2.586597020000001</v>
       </c>
       <c r="O50">
-        <v>-0.5561809088000002</v>
+        <v>-0.5690513444000002</v>
       </c>
       <c r="P50">
-        <v>-1.971914131200001</v>
+        <v>-2.017545675600001</v>
       </c>
       <c r="Q50">
-        <v>0.2080858687999996</v>
+        <v>0.1624543243999996</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.136507891211359</v>
+        <v>0.1382864773135425</v>
       </c>
       <c r="T50">
-        <v>2.094870466775036</v>
+        <v>2.135946358280429</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02193657946847837</v>
+        <v>0.0214888941732033</v>
       </c>
       <c r="W50">
-        <v>0.2306273545613328</v>
+        <v>0.2307329187539587</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.09971172485671986</v>
+        <v>0.09767679169637866</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5805,22 +5805,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1835852336193464</v>
+        <v>0.1854852336193464</v>
       </c>
       <c r="C51">
-        <v>-2.772371438492948</v>
+        <v>-3.132431260099676</v>
       </c>
       <c r="D51">
-        <v>9.384528561507052</v>
+        <v>9.272568739900326</v>
       </c>
       <c r="E51">
-        <v>-4.943100000000001</v>
+        <v>-4.695</v>
       </c>
       <c r="F51">
-        <v>12.1569</v>
+        <v>12.405</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5841,37 +5841,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M51">
-        <v>2.86659702</v>
+        <v>2.925099</v>
       </c>
       <c r="N51">
-        <v>-2.586597020000001</v>
+        <v>-2.645099000000001</v>
       </c>
       <c r="O51">
-        <v>-0.5690513444000002</v>
+        <v>-0.5819217800000002</v>
       </c>
       <c r="P51">
-        <v>-2.017545675600001</v>
+        <v>-2.06317722</v>
       </c>
       <c r="Q51">
-        <v>0.1624543243999996</v>
+        <v>0.1168227799999997</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1382864773135425</v>
+        <v>0.1401362068598134</v>
       </c>
       <c r="T51">
-        <v>2.135946358280429</v>
+        <v>2.178665285446037</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.0214888941732033</v>
+        <v>0.02105911628973924</v>
       </c>
       <c r="W51">
-        <v>0.2307329187539587</v>
+        <v>0.2308342603788795</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.09767679169637866</v>
+        <v>0.09572325586245112</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5887,22 +5887,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1854852336193464</v>
+        <v>0.1873852336193464</v>
       </c>
       <c r="C52">
-        <v>-3.132431260099676</v>
+        <v>-3.489851158158139</v>
       </c>
       <c r="D52">
-        <v>9.272568739900326</v>
+        <v>9.163248841841863</v>
       </c>
       <c r="E52">
-        <v>-4.695</v>
+        <v>-4.446899999999999</v>
       </c>
       <c r="F52">
-        <v>12.405</v>
+        <v>12.6531</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5923,37 +5923,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M52">
-        <v>2.925099</v>
+        <v>2.983600980000001</v>
       </c>
       <c r="N52">
-        <v>-2.645099000000001</v>
+        <v>-2.703600980000001</v>
       </c>
       <c r="O52">
-        <v>-0.5819217800000002</v>
+        <v>-0.5947922156000002</v>
       </c>
       <c r="P52">
-        <v>-2.06317722</v>
+        <v>-2.108808764400001</v>
       </c>
       <c r="Q52">
-        <v>0.1168227799999997</v>
+        <v>0.07119123559999929</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1401362068598134</v>
+        <v>0.1420614355712382</v>
       </c>
       <c r="T52">
-        <v>2.178665285446037</v>
+        <v>2.223127842291875</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02105911628973924</v>
+        <v>0.02064619244092082</v>
       </c>
       <c r="W52">
-        <v>0.2308342603788795</v>
+        <v>0.2309316278224309</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.09572325586245112</v>
+        <v>0.09384632927691283</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5969,22 +5969,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1873852336193464</v>
+        <v>0.1892852336193465</v>
       </c>
       <c r="C53">
-        <v>-3.489851158158139</v>
+        <v>-3.844723415635327</v>
       </c>
       <c r="D53">
-        <v>9.163248841841863</v>
+        <v>9.056476584364674</v>
       </c>
       <c r="E53">
-        <v>-4.446899999999999</v>
+        <v>-4.1988</v>
       </c>
       <c r="F53">
-        <v>12.6531</v>
+        <v>12.9012</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -6005,37 +6005,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M53">
-        <v>2.983600980000001</v>
+        <v>3.04210296</v>
       </c>
       <c r="N53">
-        <v>-2.703600980000001</v>
+        <v>-2.76210296</v>
       </c>
       <c r="O53">
-        <v>-0.5947922156000002</v>
+        <v>-0.6076626512000001</v>
       </c>
       <c r="P53">
-        <v>-2.108808764400001</v>
+        <v>-2.1544403088</v>
       </c>
       <c r="Q53">
-        <v>0.07119123559999929</v>
+        <v>0.02555969119999979</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1420614355712382</v>
+        <v>0.144066882145639</v>
       </c>
       <c r="T53">
-        <v>2.223127842291875</v>
+        <v>2.269443005672956</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02064619244092082</v>
+        <v>0.02024915027859542</v>
       </c>
       <c r="W53">
-        <v>0.2309316278224309</v>
+        <v>0.2310252503643072</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.09384632927691283</v>
+        <v>0.09204159217543373</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6051,22 +6051,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1892852336193465</v>
+        <v>0.1911852336193465</v>
       </c>
       <c r="C54">
-        <v>-3.844723415635327</v>
+        <v>-4.197136063831241</v>
       </c>
       <c r="D54">
-        <v>9.056476584364674</v>
+        <v>8.952163936168761</v>
       </c>
       <c r="E54">
-        <v>-4.1988</v>
+        <v>-3.950699999999999</v>
       </c>
       <c r="F54">
-        <v>12.9012</v>
+        <v>13.1493</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -6087,37 +6087,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M54">
-        <v>3.04210296</v>
+        <v>3.100604940000001</v>
       </c>
       <c r="N54">
-        <v>-2.76210296</v>
+        <v>-2.820604940000001</v>
       </c>
       <c r="O54">
-        <v>-0.6076626512000001</v>
+        <v>-0.6205330868000002</v>
       </c>
       <c r="P54">
-        <v>-2.1544403088</v>
+        <v>-2.200071853200001</v>
       </c>
       <c r="Q54">
-        <v>0.02555969119999979</v>
+        <v>-0.0200718532000006</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.144066882145639</v>
+        <v>0.1461576668721419</v>
       </c>
       <c r="T54">
-        <v>2.269443005672956</v>
+        <v>2.317729027070253</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02024915027859542</v>
+        <v>0.01986709083937664</v>
       </c>
       <c r="W54">
-        <v>0.2310252503643072</v>
+        <v>0.231115339980075</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.09204159217543373</v>
+        <v>0.09030495836080288</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6133,22 +6133,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1911852336193465</v>
+        <v>0.1930852336193465</v>
       </c>
       <c r="C55">
-        <v>-4.197136063831241</v>
+        <v>-4.547173124444596</v>
       </c>
       <c r="D55">
-        <v>8.952163936168761</v>
+        <v>8.850226875555407</v>
       </c>
       <c r="E55">
-        <v>-3.950699999999999</v>
+        <v>-3.702599999999999</v>
       </c>
       <c r="F55">
-        <v>13.1493</v>
+        <v>13.3974</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -6169,37 +6169,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M55">
-        <v>3.100604940000001</v>
+        <v>3.159106920000001</v>
       </c>
       <c r="N55">
-        <v>-2.820604940000001</v>
+        <v>-2.879106920000001</v>
       </c>
       <c r="O55">
-        <v>-0.6205330868000002</v>
+        <v>-0.6334035224000002</v>
       </c>
       <c r="P55">
-        <v>-2.200071853200001</v>
+        <v>-2.245703397600001</v>
       </c>
       <c r="Q55">
-        <v>-0.0200718532000006</v>
+        <v>-0.06570339760000055</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1461576668721419</v>
+        <v>0.1483393552824059</v>
       </c>
       <c r="T55">
-        <v>2.317729027070253</v>
+        <v>2.368114440702215</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.01986709083937664</v>
+        <v>0.01949918174975855</v>
       </c>
       <c r="W55">
-        <v>0.231115339980075</v>
+        <v>0.231202092943407</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.09030495836080288</v>
+        <v>0.08863264431708429</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1930852336193465</v>
+        <v>0.1949852336193465</v>
       </c>
       <c r="C56">
-        <v>-4.547173124444596</v>
+        <v>-4.894914835286569</v>
       </c>
       <c r="D56">
-        <v>8.850226875555407</v>
+        <v>8.750585164713433</v>
       </c>
       <c r="E56">
-        <v>-3.702599999999999</v>
+        <v>-3.454499999999999</v>
       </c>
       <c r="F56">
-        <v>13.3974</v>
+        <v>13.6455</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -6251,37 +6251,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M56">
-        <v>3.159106920000001</v>
+        <v>3.217608900000001</v>
       </c>
       <c r="N56">
-        <v>-2.879106920000001</v>
+        <v>-2.937608900000001</v>
       </c>
       <c r="O56">
-        <v>-0.6334035224000002</v>
+        <v>-0.6462739580000002</v>
       </c>
       <c r="P56">
-        <v>-2.245703397600001</v>
+        <v>-2.291334942000001</v>
       </c>
       <c r="Q56">
-        <v>-0.06570339760000055</v>
+        <v>-0.1113349420000005</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1483393552824059</v>
+        <v>0.1506180076220149</v>
       </c>
       <c r="T56">
-        <v>2.368114440702215</v>
+        <v>2.420739206051153</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.01949918174975855</v>
+        <v>0.01914465117249022</v>
       </c>
       <c r="W56">
-        <v>0.231202092943407</v>
+        <v>0.2312856912535268</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.08863264431708429</v>
+        <v>0.08702114169313735</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6297,22 +6297,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1949852336193465</v>
+        <v>0.1968852336193465</v>
       </c>
       <c r="C57">
-        <v>-4.894914835286569</v>
+        <v>-5.240437860916877</v>
       </c>
       <c r="D57">
-        <v>8.750585164713433</v>
+        <v>8.653162139083125</v>
       </c>
       <c r="E57">
-        <v>-3.454499999999999</v>
+        <v>-3.206399999999999</v>
       </c>
       <c r="F57">
-        <v>13.6455</v>
+        <v>13.8936</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -6333,37 +6333,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M57">
-        <v>3.217608900000001</v>
+        <v>3.276110880000001</v>
       </c>
       <c r="N57">
-        <v>-2.937608900000001</v>
+        <v>-2.996110880000001</v>
       </c>
       <c r="O57">
-        <v>-0.6462739580000002</v>
+        <v>-0.6591443936000002</v>
       </c>
       <c r="P57">
-        <v>-2.291334942000001</v>
+        <v>-2.336966486400001</v>
       </c>
       <c r="Q57">
-        <v>-0.1113349420000005</v>
+        <v>-0.1569664864000009</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1506180076220149</v>
+        <v>0.1530002350679698</v>
       </c>
       <c r="T57">
-        <v>2.420739206051153</v>
+        <v>2.475756006188679</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01914465117249022</v>
+        <v>0.01880278240155289</v>
       </c>
       <c r="W57">
-        <v>0.2312856912535268</v>
+        <v>0.2313663039097139</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.08702114169313735</v>
+        <v>0.08546719273433134</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6379,22 +6379,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1968852336193465</v>
+        <v>0.1987852336193465</v>
       </c>
       <c r="C58">
-        <v>-5.240437860916877</v>
+        <v>-5.583815489364275</v>
       </c>
       <c r="D58">
-        <v>8.653162139083125</v>
+        <v>8.557884510635729</v>
       </c>
       <c r="E58">
-        <v>-3.206399999999999</v>
+        <v>-2.958299999999998</v>
       </c>
       <c r="F58">
-        <v>13.8936</v>
+        <v>14.1417</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6415,37 +6415,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M58">
-        <v>3.276110880000001</v>
+        <v>3.334612860000001</v>
       </c>
       <c r="N58">
-        <v>-2.996110880000001</v>
+        <v>-3.054612860000001</v>
       </c>
       <c r="O58">
-        <v>-0.6591443936000002</v>
+        <v>-0.6720148292000002</v>
       </c>
       <c r="P58">
-        <v>-2.336966486400001</v>
+        <v>-2.382598030800001</v>
       </c>
       <c r="Q58">
-        <v>-0.1569664864000009</v>
+        <v>-0.2025980308000008</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1530002350679698</v>
+        <v>0.1554932637904807</v>
       </c>
       <c r="T58">
-        <v>2.475756006188679</v>
+        <v>2.533331727262834</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01880278240155289</v>
+        <v>0.01847290902608704</v>
       </c>
       <c r="W58">
-        <v>0.2313663039097139</v>
+        <v>0.2314440880516487</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.08546719273433134</v>
+        <v>0.08396776830039565</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6461,22 +6461,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1987852336193465</v>
+        <v>0.2006852336193465</v>
       </c>
       <c r="C59">
-        <v>-5.583815489364275</v>
+        <v>-5.925117815992424</v>
       </c>
       <c r="D59">
-        <v>8.557884510635729</v>
+        <v>8.464682184007579</v>
       </c>
       <c r="E59">
-        <v>-2.958299999999998</v>
+        <v>-2.710199999999999</v>
       </c>
       <c r="F59">
-        <v>14.1417</v>
+        <v>14.3898</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6497,37 +6497,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M59">
-        <v>3.334612860000001</v>
+        <v>3.393114840000001</v>
       </c>
       <c r="N59">
-        <v>-3.054612860000001</v>
+        <v>-3.113114840000001</v>
       </c>
       <c r="O59">
-        <v>-0.6720148292000002</v>
+        <v>-0.6848852648000002</v>
       </c>
       <c r="P59">
-        <v>-2.382598030800001</v>
+        <v>-2.428229575200001</v>
       </c>
       <c r="Q59">
-        <v>-0.2025980308000008</v>
+        <v>-0.2482295752000008</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1554932637904807</v>
+        <v>0.1581050081664445</v>
       </c>
       <c r="T59">
-        <v>2.533331727262834</v>
+        <v>2.59364914934052</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01847290902608704</v>
+        <v>0.01815441059460279</v>
       </c>
       <c r="W59">
-        <v>0.2314440880516487</v>
+        <v>0.2315191899817927</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.08396776830039565</v>
+        <v>0.08252004815728542</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6543,22 +6543,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2006852336193464</v>
+        <v>0.2025852336193465</v>
       </c>
       <c r="C60">
-        <v>-5.92511781599242</v>
+        <v>-6.264411915480494</v>
       </c>
       <c r="D60">
-        <v>8.464682184007581</v>
+        <v>8.373488084519506</v>
       </c>
       <c r="E60">
-        <v>-2.7102</v>
+        <v>-2.462100000000001</v>
       </c>
       <c r="F60">
-        <v>14.3898</v>
+        <v>14.6379</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6579,37 +6579,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M60">
-        <v>3.39311484</v>
+        <v>3.45161682</v>
       </c>
       <c r="N60">
-        <v>-3.113114840000001</v>
+        <v>-3.171616820000001</v>
       </c>
       <c r="O60">
-        <v>-0.6848852648000001</v>
+        <v>-0.6977557004000001</v>
       </c>
       <c r="P60">
-        <v>-2.4282295752</v>
+        <v>-2.4738611196</v>
       </c>
       <c r="Q60">
-        <v>-0.2482295752000003</v>
+        <v>-0.2938611196000003</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1581050081664445</v>
+        <v>0.1608441547070895</v>
       </c>
       <c r="T60">
-        <v>2.59364914934052</v>
+        <v>2.65690888469029</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01815441059460279</v>
+        <v>0.017846708720118</v>
       </c>
       <c r="W60">
-        <v>0.2315191899817927</v>
+        <v>0.2315917460837962</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.08252004815728542</v>
+        <v>0.08112140327326367</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6625,22 +6625,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2025852336193465</v>
+        <v>0.2044852336193465</v>
       </c>
       <c r="C61">
-        <v>-6.264411915480494</v>
+        <v>-6.601762002805252</v>
       </c>
       <c r="D61">
-        <v>8.373488084519506</v>
+        <v>8.284237997194749</v>
       </c>
       <c r="E61">
-        <v>-2.462100000000001</v>
+        <v>-2.214</v>
       </c>
       <c r="F61">
-        <v>14.6379</v>
+        <v>14.886</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6661,37 +6661,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M61">
-        <v>3.45161682</v>
+        <v>3.5101188</v>
       </c>
       <c r="N61">
-        <v>-3.171616820000001</v>
+        <v>-3.230118800000001</v>
       </c>
       <c r="O61">
-        <v>-0.6977557004000001</v>
+        <v>-0.7106261360000001</v>
       </c>
       <c r="P61">
-        <v>-2.4738611196</v>
+        <v>-2.519492664</v>
       </c>
       <c r="Q61">
-        <v>-0.2938611196000003</v>
+        <v>-0.3394926640000002</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1608441547070895</v>
+        <v>0.1637202585747667</v>
       </c>
       <c r="T61">
-        <v>2.65690888469029</v>
+        <v>2.723331606807546</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.017846708720118</v>
+        <v>0.0175492635747827</v>
       </c>
       <c r="W61">
-        <v>0.2315917460837962</v>
+        <v>0.2316618836490663</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.08112140327326367</v>
+        <v>0.07976937988537591</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6707,22 +6707,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2044852336193465</v>
+        <v>0.2063852336193465</v>
       </c>
       <c r="C62">
-        <v>-6.601762002805252</v>
+        <v>-6.937229584036659</v>
       </c>
       <c r="D62">
-        <v>8.284237997194749</v>
+        <v>8.196870415963343</v>
       </c>
       <c r="E62">
-        <v>-2.214</v>
+        <v>-1.9659</v>
       </c>
       <c r="F62">
-        <v>14.886</v>
+        <v>15.1341</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6743,37 +6743,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M62">
-        <v>3.5101188</v>
+        <v>3.568620780000001</v>
       </c>
       <c r="N62">
-        <v>-3.230118800000001</v>
+        <v>-3.288620780000001</v>
       </c>
       <c r="O62">
-        <v>-0.7106261360000001</v>
+        <v>-0.7234965716000002</v>
       </c>
       <c r="P62">
-        <v>-2.519492664</v>
+        <v>-2.565124208400001</v>
       </c>
       <c r="Q62">
-        <v>-0.3394926640000002</v>
+        <v>-0.3851242084000006</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1637202585747667</v>
+        <v>0.1667438549484787</v>
       </c>
       <c r="T62">
-        <v>2.723331606807546</v>
+        <v>2.793160622366714</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0175492635747827</v>
+        <v>0.01726157072929446</v>
       </c>
       <c r="W62">
-        <v>0.2316618836490663</v>
+        <v>0.2317297216220324</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.07976937988537591</v>
+        <v>0.07846168513315666</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6789,22 +6789,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2063852336193465</v>
+        <v>0.2082852336193464</v>
       </c>
       <c r="C63">
-        <v>-6.937229584036659</v>
+        <v>-7.270873597691038</v>
       </c>
       <c r="D63">
-        <v>8.196870415963343</v>
+        <v>8.111326402308963</v>
       </c>
       <c r="E63">
-        <v>-1.9659</v>
+        <v>-1.7178</v>
       </c>
       <c r="F63">
-        <v>15.1341</v>
+        <v>15.3822</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6825,37 +6825,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M63">
-        <v>3.568620780000001</v>
+        <v>3.62712276</v>
       </c>
       <c r="N63">
-        <v>-3.288620780000001</v>
+        <v>-3.34712276</v>
       </c>
       <c r="O63">
-        <v>-0.7234965716000002</v>
+        <v>-0.7363670072000001</v>
       </c>
       <c r="P63">
-        <v>-2.565124208400001</v>
+        <v>-2.6107557528</v>
       </c>
       <c r="Q63">
-        <v>-0.3851242084000006</v>
+        <v>-0.4307557528000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1667438549484787</v>
+        <v>0.1699265879734387</v>
       </c>
       <c r="T63">
-        <v>2.793160622366714</v>
+        <v>2.866664849271102</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01726157072929446</v>
+        <v>0.0169831582981768</v>
       </c>
       <c r="W63">
-        <v>0.2317297216220324</v>
+        <v>0.2317953712732899</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.07846168513315666</v>
+        <v>0.0771961740826218</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6871,22 +6871,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2082852336193464</v>
+        <v>0.2101852336193464</v>
       </c>
       <c r="C64">
-        <v>-7.270873597691038</v>
+        <v>-7.60275054732459</v>
       </c>
       <c r="D64">
-        <v>8.111326402308963</v>
+        <v>8.027549452675412</v>
       </c>
       <c r="E64">
-        <v>-1.7178</v>
+        <v>-1.4697</v>
       </c>
       <c r="F64">
-        <v>15.3822</v>
+        <v>15.6303</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6907,37 +6907,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M64">
-        <v>3.62712276</v>
+        <v>3.685624740000001</v>
       </c>
       <c r="N64">
-        <v>-3.34712276</v>
+        <v>-3.405624740000001</v>
       </c>
       <c r="O64">
-        <v>-0.7363670072000001</v>
+        <v>-0.7492374428000002</v>
       </c>
       <c r="P64">
-        <v>-2.6107557528</v>
+        <v>-2.656387297200001</v>
       </c>
       <c r="Q64">
-        <v>-0.4307557528000001</v>
+        <v>-0.4763872972000005</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1699265879734387</v>
+        <v>0.1732813606213695</v>
       </c>
       <c r="T64">
-        <v>2.866664849271102</v>
+        <v>2.94414227762978</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0169831582981768</v>
+        <v>0.0167135843569359</v>
       </c>
       <c r="W64">
-        <v>0.2317953712732899</v>
+        <v>0.2318589368086345</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.0771961740826218</v>
+        <v>0.07597083798607229</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6953,22 +6953,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2101852336193464</v>
+        <v>0.2120852336193464</v>
       </c>
       <c r="C65">
-        <v>-7.60275054732459</v>
+        <v>-7.932914625993981</v>
       </c>
       <c r="D65">
-        <v>8.027549452675412</v>
+        <v>7.94548537400602</v>
       </c>
       <c r="E65">
-        <v>-1.4697</v>
+        <v>-1.2216</v>
       </c>
       <c r="F65">
-        <v>15.6303</v>
+        <v>15.8784</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6989,37 +6989,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M65">
-        <v>3.685624740000001</v>
+        <v>3.744126720000001</v>
       </c>
       <c r="N65">
-        <v>-3.405624740000001</v>
+        <v>-3.464126720000001</v>
       </c>
       <c r="O65">
-        <v>-0.7492374428000002</v>
+        <v>-0.7621078784000002</v>
       </c>
       <c r="P65">
-        <v>-2.656387297200001</v>
+        <v>-2.702018841600001</v>
       </c>
       <c r="Q65">
-        <v>-0.4763872972000005</v>
+        <v>-0.5220188416000004</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1732813606213695</v>
+        <v>0.1768225095275186</v>
       </c>
       <c r="T65">
-        <v>2.94414227762978</v>
+        <v>3.02592400756394</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.0167135843569359</v>
+        <v>0.01645243460135878</v>
       </c>
       <c r="W65">
-        <v>0.2318589368086345</v>
+        <v>0.2319205159209996</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.07597083798607229</v>
+        <v>0.07478379364253995</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7035,22 +7035,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2120852336193464</v>
+        <v>0.2139852336193465</v>
       </c>
       <c r="C66">
-        <v>-7.932914625993981</v>
+        <v>-8.261417833160234</v>
       </c>
       <c r="D66">
-        <v>7.94548537400602</v>
+        <v>7.865082166839769</v>
       </c>
       <c r="E66">
-        <v>-1.2216</v>
+        <v>-0.9734999999999978</v>
       </c>
       <c r="F66">
-        <v>15.8784</v>
+        <v>16.1265</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -7071,37 +7071,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M66">
-        <v>3.744126720000001</v>
+        <v>3.802628700000001</v>
       </c>
       <c r="N66">
-        <v>-3.464126720000001</v>
+        <v>-3.522628700000001</v>
       </c>
       <c r="O66">
-        <v>-0.7621078784000002</v>
+        <v>-0.7749783140000003</v>
       </c>
       <c r="P66">
-        <v>-2.702018841600001</v>
+        <v>-2.747650386000001</v>
       </c>
       <c r="Q66">
-        <v>-0.5220188416000004</v>
+        <v>-0.5676503860000008</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1768225095275186</v>
+        <v>0.1805660097997335</v>
       </c>
       <c r="T66">
-        <v>3.02592400756394</v>
+        <v>3.112378979208625</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01645243460135878</v>
+        <v>0.01619932022287633</v>
       </c>
       <c r="W66">
-        <v>0.2319205159209996</v>
+        <v>0.2319802002914458</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.07478379364253995</v>
+        <v>0.07363327374034701</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7117,22 +7117,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2139852336193465</v>
+        <v>0.2158852336193465</v>
       </c>
       <c r="C67">
-        <v>-8.261417833160234</v>
+        <v>-8.5883100845657</v>
       </c>
       <c r="D67">
-        <v>7.865082166839769</v>
+        <v>7.786289915434301</v>
       </c>
       <c r="E67">
-        <v>-0.9734999999999978</v>
+        <v>-0.7254000000000005</v>
       </c>
       <c r="F67">
-        <v>16.1265</v>
+        <v>16.3746</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -7153,37 +7153,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M67">
-        <v>3.802628700000001</v>
+        <v>3.86113068</v>
       </c>
       <c r="N67">
-        <v>-3.522628700000001</v>
+        <v>-3.581130680000001</v>
       </c>
       <c r="O67">
-        <v>-0.7749783140000003</v>
+        <v>-0.7878487496000002</v>
       </c>
       <c r="P67">
-        <v>-2.747650386000001</v>
+        <v>-2.793281930400001</v>
       </c>
       <c r="Q67">
-        <v>-0.5676503860000008</v>
+        <v>-0.6132819304000003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1805660097997335</v>
+        <v>0.1845297159703138</v>
       </c>
       <c r="T67">
-        <v>3.112378979208625</v>
+        <v>3.203919537420643</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01619932022287633</v>
+        <v>0.01595387597707518</v>
       </c>
       <c r="W67">
-        <v>0.2319802002914458</v>
+        <v>0.2320380760446057</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.07363327374034701</v>
+        <v>0.07251761807761448</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7199,22 +7199,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2158852336193465</v>
+        <v>0.2177852336193465</v>
       </c>
       <c r="C68">
-        <v>-8.5883100845657</v>
+        <v>-8.913639315572134</v>
       </c>
       <c r="D68">
-        <v>7.786289915434301</v>
+        <v>7.709060684427869</v>
       </c>
       <c r="E68">
-        <v>-0.7254000000000005</v>
+        <v>-0.4772999999999996</v>
       </c>
       <c r="F68">
-        <v>16.3746</v>
+        <v>16.6227</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -7235,37 +7235,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M68">
-        <v>3.86113068</v>
+        <v>3.91963266</v>
       </c>
       <c r="N68">
-        <v>-3.581130680000001</v>
+        <v>-3.639632660000001</v>
       </c>
       <c r="O68">
-        <v>-0.7878487496000002</v>
+        <v>-0.8007191852000002</v>
       </c>
       <c r="P68">
-        <v>-2.793281930400001</v>
+        <v>-2.8389134748</v>
       </c>
       <c r="Q68">
-        <v>-0.6132819304000003</v>
+        <v>-0.6589134748000003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1845297159703138</v>
+        <v>0.1887336467572931</v>
       </c>
       <c r="T68">
-        <v>3.203919537420643</v>
+        <v>3.301008008251572</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01595387597707518</v>
+        <v>0.01571575842517853</v>
       </c>
       <c r="W68">
-        <v>0.2320380760446057</v>
+        <v>0.2320942241633429</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.07251761807761448</v>
+        <v>0.07143526556899338</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7281,22 +7281,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2177852336193465</v>
+        <v>0.2196852336193465</v>
       </c>
       <c r="C69">
-        <v>-8.913639315572134</v>
+        <v>-9.237451578409287</v>
       </c>
       <c r="D69">
-        <v>7.709060684427869</v>
+        <v>7.633348421590716</v>
       </c>
       <c r="E69">
-        <v>-0.4772999999999996</v>
+        <v>-0.2291999999999987</v>
       </c>
       <c r="F69">
-        <v>16.6227</v>
+        <v>16.8708</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -7317,37 +7317,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M69">
-        <v>3.91963266</v>
+        <v>3.978134640000001</v>
       </c>
       <c r="N69">
-        <v>-3.639632660000001</v>
+        <v>-3.698134640000001</v>
       </c>
       <c r="O69">
-        <v>-0.8007191852000002</v>
+        <v>-0.8135896208000002</v>
       </c>
       <c r="P69">
-        <v>-2.8389134748</v>
+        <v>-2.884545019200001</v>
       </c>
       <c r="Q69">
-        <v>-0.6589134748000003</v>
+        <v>-0.7045450192000007</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1887336467572931</v>
+        <v>0.1932003232184585</v>
       </c>
       <c r="T69">
-        <v>3.301008008251572</v>
+        <v>3.404164508509433</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01571575842517853</v>
+        <v>0.01548464433069061</v>
       </c>
       <c r="W69">
-        <v>0.2320942241633429</v>
+        <v>0.2321487208668232</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.07143526556899338</v>
+        <v>0.0703847469576846</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7363,22 +7363,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2196852336193465</v>
+        <v>0.2215852336193465</v>
       </c>
       <c r="C70">
-        <v>-9.237451578409287</v>
+        <v>-9.559791133748671</v>
       </c>
       <c r="D70">
-        <v>7.633348421590716</v>
+        <v>7.559108866251331</v>
       </c>
       <c r="E70">
-        <v>-0.2291999999999987</v>
+        <v>0.01890000000000214</v>
       </c>
       <c r="F70">
-        <v>16.8708</v>
+        <v>17.1189</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7399,37 +7399,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M70">
-        <v>3.978134640000001</v>
+        <v>4.036636620000001</v>
       </c>
       <c r="N70">
-        <v>-3.698134640000001</v>
+        <v>-3.756636620000001</v>
       </c>
       <c r="O70">
-        <v>-0.8135896208000002</v>
+        <v>-0.8264600564000003</v>
       </c>
       <c r="P70">
-        <v>-2.884545019200001</v>
+        <v>-2.930176563600001</v>
       </c>
       <c r="Q70">
-        <v>-0.7045450192000007</v>
+        <v>-0.7501765636000011</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1932003232184585</v>
+        <v>0.1979551723545378</v>
       </c>
       <c r="T70">
-        <v>3.404164508509433</v>
+        <v>3.513976266848448</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01548464433069061</v>
+        <v>0.01526022919546321</v>
       </c>
       <c r="W70">
-        <v>0.2321487208668232</v>
+        <v>0.2322016379557098</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.0703847469576846</v>
+        <v>0.0693646781611964</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7445,22 +7445,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2215852336193465</v>
+        <v>0.2234852336193465</v>
       </c>
       <c r="C71">
-        <v>-9.559791133748671</v>
+        <v>-9.880700536985096</v>
       </c>
       <c r="D71">
-        <v>7.559108866251331</v>
+        <v>7.486299463014909</v>
       </c>
       <c r="E71">
-        <v>0.01890000000000214</v>
+        <v>0.267000000000003</v>
       </c>
       <c r="F71">
-        <v>17.1189</v>
+        <v>17.367</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7481,37 +7481,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M71">
-        <v>4.036636620000001</v>
+        <v>4.095138600000001</v>
       </c>
       <c r="N71">
-        <v>-3.756636620000001</v>
+        <v>-3.815138600000001</v>
       </c>
       <c r="O71">
-        <v>-0.8264600564000003</v>
+        <v>-0.8393304920000003</v>
       </c>
       <c r="P71">
-        <v>-2.930176563600001</v>
+        <v>-2.975808108000001</v>
       </c>
       <c r="Q71">
-        <v>-0.7501765636000011</v>
+        <v>-0.795808108000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1979551723545378</v>
+        <v>0.2030270114330224</v>
       </c>
       <c r="T71">
-        <v>3.513976266848448</v>
+        <v>3.631108809076729</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01526022919546321</v>
+        <v>0.01504222592124231</v>
       </c>
       <c r="W71">
-        <v>0.2322016379557098</v>
+        <v>0.2322530431277711</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.0693646781611964</v>
+        <v>0.06837375418746505</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7527,22 +7527,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2234852336193465</v>
+        <v>0.2253852336193465</v>
       </c>
       <c r="C72">
-        <v>-9.880700536985096</v>
+        <v>-10.20022071957935</v>
       </c>
       <c r="D72">
-        <v>7.486299463014909</v>
+        <v>7.414879280420653</v>
       </c>
       <c r="E72">
-        <v>0.267000000000003</v>
+        <v>0.5151000000000003</v>
       </c>
       <c r="F72">
-        <v>17.367</v>
+        <v>17.6151</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7563,37 +7563,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M72">
-        <v>4.095138600000001</v>
+        <v>4.15364058</v>
       </c>
       <c r="N72">
-        <v>-3.815138600000001</v>
+        <v>-3.87364058</v>
       </c>
       <c r="O72">
-        <v>-0.8393304920000003</v>
+        <v>-0.8522009276000001</v>
       </c>
       <c r="P72">
-        <v>-2.975808108000001</v>
+        <v>-3.0214396524</v>
       </c>
       <c r="Q72">
-        <v>-0.795808108000001</v>
+        <v>-0.8414396524000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2030270114330224</v>
+        <v>0.2084486325169197</v>
       </c>
       <c r="T72">
-        <v>3.631108809076729</v>
+        <v>3.756319457665583</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01504222592124231</v>
+        <v>0.0148303635843234</v>
       </c>
       <c r="W72">
-        <v>0.2322530431277711</v>
+        <v>0.2323030002668166</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.06837375418746505</v>
+        <v>0.06741074356510635</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7609,22 +7609,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2253852336193465</v>
+        <v>0.2272852336193465</v>
       </c>
       <c r="C73">
-        <v>-10.20022071957935</v>
+        <v>-10.51839106578883</v>
       </c>
       <c r="D73">
-        <v>7.414879280420653</v>
+        <v>7.344808934211174</v>
       </c>
       <c r="E73">
-        <v>0.5151000000000003</v>
+        <v>0.7632000000000012</v>
       </c>
       <c r="F73">
-        <v>17.6151</v>
+        <v>17.8632</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7645,37 +7645,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M73">
-        <v>4.15364058</v>
+        <v>4.212142560000001</v>
       </c>
       <c r="N73">
-        <v>-3.87364058</v>
+        <v>-3.932142560000001</v>
       </c>
       <c r="O73">
-        <v>-0.8522009276000001</v>
+        <v>-0.8650713632000003</v>
       </c>
       <c r="P73">
-        <v>-3.0214396524</v>
+        <v>-3.067071196800001</v>
       </c>
       <c r="Q73">
-        <v>-0.8414396524000001</v>
+        <v>-0.8870711968000009</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2084486325169197</v>
+        <v>0.2142575122496668</v>
       </c>
       <c r="T73">
-        <v>3.756319457665581</v>
+        <v>3.890473724010781</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0148303635843234</v>
+        <v>0.01462438631231891</v>
       </c>
       <c r="W73">
-        <v>0.2323030002668166</v>
+        <v>0.2323515697075552</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.06741074356510635</v>
+        <v>0.06647448323781324</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7691,22 +7691,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2272852336193465</v>
+        <v>0.2291852336193465</v>
       </c>
       <c r="C74">
-        <v>-10.51839106578883</v>
+        <v>-10.83524948508822</v>
       </c>
       <c r="D74">
-        <v>7.344808934211174</v>
+        <v>7.276050514911783</v>
       </c>
       <c r="E74">
-        <v>0.7632000000000012</v>
+        <v>1.011299999999999</v>
       </c>
       <c r="F74">
-        <v>17.8632</v>
+        <v>18.1113</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7727,37 +7727,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M74">
-        <v>4.212142560000001</v>
+        <v>4.27064454</v>
       </c>
       <c r="N74">
-        <v>-3.932142560000001</v>
+        <v>-3.99064454</v>
       </c>
       <c r="O74">
-        <v>-0.8650713632000003</v>
+        <v>-0.8779417988000001</v>
       </c>
       <c r="P74">
-        <v>-3.067071196800001</v>
+        <v>-3.1127027412</v>
       </c>
       <c r="Q74">
-        <v>-0.8870711968000009</v>
+        <v>-0.9327027412</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2142575122496668</v>
+        <v>0.2204966793700248</v>
       </c>
       <c r="T74">
-        <v>3.890473724010781</v>
+        <v>4.034565343418588</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01462438631231891</v>
+        <v>0.01442405225324605</v>
       </c>
       <c r="W74">
-        <v>0.2323515697075552</v>
+        <v>0.2323988084786846</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.06647448323781324</v>
+        <v>0.06556387387839113</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7773,22 +7773,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2291852336193465</v>
+        <v>0.2310852336193465</v>
       </c>
       <c r="C75">
-        <v>-10.83524948508822</v>
+        <v>-11.15083248056015</v>
       </c>
       <c r="D75">
-        <v>7.276050514911783</v>
+        <v>7.208567519439845</v>
       </c>
       <c r="E75">
-        <v>1.011299999999999</v>
+        <v>1.259399999999999</v>
       </c>
       <c r="F75">
-        <v>18.1113</v>
+        <v>18.3594</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7809,37 +7809,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M75">
-        <v>4.27064454</v>
+        <v>4.32914652</v>
       </c>
       <c r="N75">
-        <v>-3.99064454</v>
+        <v>-4.049146520000001</v>
       </c>
       <c r="O75">
-        <v>-0.8779417988000001</v>
+        <v>-0.8908122344000001</v>
       </c>
       <c r="P75">
-        <v>-3.1127027412</v>
+        <v>-3.158334285600001</v>
       </c>
       <c r="Q75">
-        <v>-0.9327027412</v>
+        <v>-0.9783342856000004</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2204966793700248</v>
+        <v>0.2272157824227181</v>
       </c>
       <c r="T75">
-        <v>4.034565343418588</v>
+        <v>4.189740933550071</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01442405225324605</v>
+        <v>0.01422913262820219</v>
       </c>
       <c r="W75">
-        <v>0.2323988084786846</v>
+        <v>0.2324447705262699</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.06556387387839113</v>
+        <v>0.06467787558273708</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7855,22 +7855,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2310852336193465</v>
+        <v>0.2329852336193464</v>
       </c>
       <c r="C76">
-        <v>-11.15083248056015</v>
+        <v>-11.46517521351503</v>
       </c>
       <c r="D76">
-        <v>7.208567519439845</v>
+        <v>7.142324786484973</v>
       </c>
       <c r="E76">
-        <v>1.259399999999999</v>
+        <v>1.5075</v>
       </c>
       <c r="F76">
-        <v>18.3594</v>
+        <v>18.6075</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7891,37 +7891,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M76">
-        <v>4.32914652</v>
+        <v>4.387648500000001</v>
       </c>
       <c r="N76">
-        <v>-4.049146520000001</v>
+        <v>-4.107648500000002</v>
       </c>
       <c r="O76">
-        <v>-0.8908122344000001</v>
+        <v>-0.9036826700000004</v>
       </c>
       <c r="P76">
-        <v>-3.158334285600001</v>
+        <v>-3.203965830000001</v>
       </c>
       <c r="Q76">
-        <v>-0.9783342856000004</v>
+        <v>-1.023965830000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2272157824227181</v>
+        <v>0.2344724137196268</v>
       </c>
       <c r="T76">
-        <v>4.189740933550071</v>
+        <v>4.357330570892074</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01422913262820219</v>
+        <v>0.01403941085982616</v>
       </c>
       <c r="W76">
-        <v>0.2324447705262699</v>
+        <v>0.232489506919253</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.06467787558273708</v>
+        <v>0.0638155039083006</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7937,22 +7937,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2329852336193464</v>
+        <v>0.2348852336193465</v>
       </c>
       <c r="C77">
-        <v>-11.46517521351503</v>
+        <v>-11.77831156458032</v>
       </c>
       <c r="D77">
-        <v>7.142324786484973</v>
+        <v>7.077288435419685</v>
       </c>
       <c r="E77">
-        <v>1.5075</v>
+        <v>1.755600000000001</v>
       </c>
       <c r="F77">
-        <v>18.6075</v>
+        <v>18.8556</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7973,37 +7973,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M77">
-        <v>4.387648500000001</v>
+        <v>4.446150480000001</v>
       </c>
       <c r="N77">
-        <v>-4.107648500000002</v>
+        <v>-4.166150480000001</v>
       </c>
       <c r="O77">
-        <v>-0.9036826700000004</v>
+        <v>-0.9165531056000001</v>
       </c>
       <c r="P77">
-        <v>-3.203965830000001</v>
+        <v>-3.2495973744</v>
       </c>
       <c r="Q77">
-        <v>-1.023965830000001</v>
+        <v>-1.0695973744</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2344724137196268</v>
+        <v>0.242333764291278</v>
       </c>
       <c r="T77">
-        <v>4.357330570892074</v>
+        <v>4.538886011345912</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01403941085982616</v>
+        <v>0.01385468176956529</v>
       </c>
       <c r="W77">
-        <v>0.232489506919253</v>
+        <v>0.2325330660387365</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.0638155039083006</v>
+        <v>0.06297582622529685</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8019,22 +8019,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2348852336193465</v>
+        <v>0.2367852336193464</v>
       </c>
       <c r="C78">
-        <v>-11.77831156458032</v>
+        <v>-12.09027419148244</v>
       </c>
       <c r="D78">
-        <v>7.077288435419685</v>
+        <v>7.013425808517562</v>
       </c>
       <c r="E78">
-        <v>1.755600000000001</v>
+        <v>2.003700000000002</v>
       </c>
       <c r="F78">
-        <v>18.8556</v>
+        <v>19.1037</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -8055,37 +8055,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M78">
-        <v>4.446150480000001</v>
+        <v>4.504652460000001</v>
       </c>
       <c r="N78">
-        <v>-4.166150480000001</v>
+        <v>-4.224652460000001</v>
       </c>
       <c r="O78">
-        <v>-0.9165531056000001</v>
+        <v>-0.9294235412000004</v>
       </c>
       <c r="P78">
-        <v>-3.2495973744</v>
+        <v>-3.295228918800001</v>
       </c>
       <c r="Q78">
-        <v>-1.0695973744</v>
+        <v>-1.115228918800001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.242333764291278</v>
+        <v>0.2508787105648118</v>
       </c>
       <c r="T78">
-        <v>4.538886011345912</v>
+        <v>4.736228881404429</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01385468176956529</v>
+        <v>0.01367475083749301</v>
       </c>
       <c r="W78">
-        <v>0.2325330660387365</v>
+        <v>0.2325754937525192</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.06297582622529685</v>
+        <v>0.06215795835224081</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8101,22 +8101,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2367852336193464</v>
+        <v>0.2386852336193465</v>
       </c>
       <c r="C79">
-        <v>-12.09027419148244</v>
+        <v>-12.40109458372821</v>
       </c>
       <c r="D79">
-        <v>7.013425808517562</v>
+        <v>6.950705416271794</v>
       </c>
       <c r="E79">
-        <v>2.003700000000002</v>
+        <v>2.251799999999999</v>
       </c>
       <c r="F79">
-        <v>19.1037</v>
+        <v>19.3518</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -8137,37 +8137,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M79">
-        <v>4.504652460000001</v>
+        <v>4.563154440000001</v>
       </c>
       <c r="N79">
-        <v>-4.224652460000001</v>
+        <v>-4.283154440000001</v>
       </c>
       <c r="O79">
-        <v>-0.9294235412000004</v>
+        <v>-0.9422939768000002</v>
       </c>
       <c r="P79">
-        <v>-3.295228918800001</v>
+        <v>-3.3408604632</v>
       </c>
       <c r="Q79">
-        <v>-1.115228918800001</v>
+        <v>-1.1608604632</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2508787105648118</v>
+        <v>0.2602004701359396</v>
       </c>
       <c r="T79">
-        <v>4.736228881404429</v>
+        <v>4.951512012377358</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01367475083749301</v>
+        <v>0.01349943351906361</v>
       </c>
       <c r="W79">
-        <v>0.2325754937525192</v>
+        <v>0.2326168335762048</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.06215795835224081</v>
+        <v>0.06136106145028919</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8183,22 +8183,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2386852336193465</v>
+        <v>0.2405852336193464</v>
       </c>
       <c r="C80">
-        <v>-12.40109458372821</v>
+        <v>-12.71080311437817</v>
       </c>
       <c r="D80">
-        <v>6.950705416271794</v>
+        <v>6.889096885621832</v>
       </c>
       <c r="E80">
-        <v>2.251799999999999</v>
+        <v>2.4999</v>
       </c>
       <c r="F80">
-        <v>19.3518</v>
+        <v>19.5999</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -8219,37 +8219,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M80">
-        <v>4.563154440000001</v>
+        <v>4.621656420000001</v>
       </c>
       <c r="N80">
-        <v>-4.283154440000001</v>
+        <v>-4.341656420000001</v>
       </c>
       <c r="O80">
-        <v>-0.9422939768000002</v>
+        <v>-0.9551644124000003</v>
       </c>
       <c r="P80">
-        <v>-3.3408604632</v>
+        <v>-3.386492007600001</v>
       </c>
       <c r="Q80">
-        <v>-1.1608604632</v>
+        <v>-1.206492007600001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2602004701359396</v>
+        <v>0.2704100163328891</v>
       </c>
       <c r="T80">
-        <v>4.951512012377358</v>
+        <v>5.187298298681041</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01349943351906361</v>
+        <v>0.01332855461375901</v>
       </c>
       <c r="W80">
-        <v>0.2326168335762048</v>
+        <v>0.2326571268220756</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.06136106145028919</v>
+        <v>0.06058433915344996</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8265,22 +8265,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2405852336193464</v>
+        <v>0.2424852336193465</v>
       </c>
       <c r="C81">
-        <v>-12.71080311437817</v>
+        <v>-13.0194290890908</v>
       </c>
       <c r="D81">
-        <v>6.889096885621832</v>
+        <v>6.828570910909204</v>
       </c>
       <c r="E81">
-        <v>2.4999</v>
+        <v>2.748000000000001</v>
       </c>
       <c r="F81">
-        <v>19.5999</v>
+        <v>19.848</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -8301,37 +8301,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M81">
-        <v>4.621656420000001</v>
+        <v>4.680158400000001</v>
       </c>
       <c r="N81">
-        <v>-4.341656420000001</v>
+        <v>-4.4001584</v>
       </c>
       <c r="O81">
-        <v>-0.9551644124000003</v>
+        <v>-0.9680348480000001</v>
       </c>
       <c r="P81">
-        <v>-3.386492007600001</v>
+        <v>-3.432123552</v>
       </c>
       <c r="Q81">
-        <v>-1.206492007600001</v>
+        <v>-1.252123552</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2704100163328891</v>
+        <v>0.2816405171495336</v>
       </c>
       <c r="T81">
-        <v>5.187298298681041</v>
+        <v>5.446663213615095</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01332855461375901</v>
+        <v>0.01316194768108702</v>
       </c>
       <c r="W81">
-        <v>0.2326571268220756</v>
+        <v>0.2326964127367997</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.06058433915344996</v>
+        <v>0.05982703491403196</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8347,22 +8347,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2424852336193465</v>
+        <v>0.2443852336193465</v>
       </c>
       <c r="C82">
-        <v>-13.0194290890908</v>
+        <v>-13.32700079260381</v>
       </c>
       <c r="D82">
-        <v>6.828570910909204</v>
+        <v>6.769099207396191</v>
       </c>
       <c r="E82">
-        <v>2.748000000000001</v>
+        <v>2.996100000000002</v>
       </c>
       <c r="F82">
-        <v>19.848</v>
+        <v>20.0961</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8383,37 +8383,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M82">
-        <v>4.680158400000001</v>
+        <v>4.738660380000001</v>
       </c>
       <c r="N82">
-        <v>-4.4001584</v>
+        <v>-4.458660380000001</v>
       </c>
       <c r="O82">
-        <v>-0.9680348480000001</v>
+        <v>-0.9809052836000003</v>
       </c>
       <c r="P82">
-        <v>-3.432123552</v>
+        <v>-3.477755096400001</v>
       </c>
       <c r="Q82">
-        <v>-1.252123552</v>
+        <v>-1.297755096400001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2816405171495336</v>
+        <v>0.2940531759468775</v>
       </c>
       <c r="T82">
-        <v>5.446663213615095</v>
+        <v>5.733329698542205</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01316194768108702</v>
+        <v>0.01299945449983903</v>
       </c>
       <c r="W82">
-        <v>0.2326964127367997</v>
+        <v>0.232734728628938</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.05982703491403196</v>
+        <v>0.05908842954472282</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8429,22 +8429,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2443852336193465</v>
+        <v>0.2462852336193465</v>
       </c>
       <c r="C83">
-        <v>-13.32700079260381</v>
+        <v>-13.63354553280759</v>
       </c>
       <c r="D83">
-        <v>6.769099207396191</v>
+        <v>6.710654467192414</v>
       </c>
       <c r="E83">
-        <v>2.996100000000002</v>
+        <v>3.244200000000003</v>
       </c>
       <c r="F83">
-        <v>20.0961</v>
+        <v>20.3442</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8465,37 +8465,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M83">
-        <v>4.738660380000001</v>
+        <v>4.797162360000002</v>
       </c>
       <c r="N83">
-        <v>-4.458660380000001</v>
+        <v>-4.517162360000002</v>
       </c>
       <c r="O83">
-        <v>-0.9809052836000003</v>
+        <v>-0.9937757192000005</v>
       </c>
       <c r="P83">
-        <v>-3.477755096400001</v>
+        <v>-3.523386640800002</v>
       </c>
       <c r="Q83">
-        <v>-1.297755096400001</v>
+        <v>-1.343386640800002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2940531759468775</v>
+        <v>0.3078450190550373</v>
       </c>
       <c r="T83">
-        <v>5.733329698542205</v>
+        <v>6.051848015127883</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01299945449983903</v>
+        <v>0.01284092456691417</v>
       </c>
       <c r="W83">
-        <v>0.232734728628938</v>
+        <v>0.2327721099871216</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.05908842954472282</v>
+        <v>0.05836783894051889</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8511,22 +8511,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2462852336193465</v>
+        <v>0.2481852336193465</v>
       </c>
       <c r="C84">
-        <v>-13.63354553280759</v>
+        <v>-13.93908968255491</v>
       </c>
       <c r="D84">
-        <v>6.710654467192414</v>
+        <v>6.653210317445089</v>
       </c>
       <c r="E84">
-        <v>3.244200000000003</v>
+        <v>3.492300000000004</v>
       </c>
       <c r="F84">
-        <v>20.3442</v>
+        <v>20.59230000000001</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8547,37 +8547,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M84">
-        <v>4.797162360000002</v>
+        <v>4.855664340000001</v>
       </c>
       <c r="N84">
-        <v>-4.517162360000002</v>
+        <v>-4.575664340000001</v>
       </c>
       <c r="O84">
-        <v>-0.9937757192000005</v>
+        <v>-1.0066461548</v>
       </c>
       <c r="P84">
-        <v>-3.523386640800002</v>
+        <v>-3.569018185200001</v>
       </c>
       <c r="Q84">
-        <v>-1.343386640800002</v>
+        <v>-1.389018185200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3078450190550373</v>
+        <v>0.3232594319406278</v>
       </c>
       <c r="T84">
-        <v>6.051848015127883</v>
+        <v>6.407839074841288</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01284092456691417</v>
+        <v>0.01268621463237303</v>
       </c>
       <c r="W84">
-        <v>0.2327721099871216</v>
+        <v>0.2328085905896864</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.05836783894051889</v>
+        <v>0.05766461196533201</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8593,22 +8593,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2481852336193465</v>
+        <v>0.2500852336193465</v>
       </c>
       <c r="C85">
-        <v>-13.93908968255491</v>
+        <v>-14.24365871934158</v>
       </c>
       <c r="D85">
-        <v>6.653210317445089</v>
+        <v>6.596741280658422</v>
       </c>
       <c r="E85">
-        <v>3.492300000000004</v>
+        <v>3.740400000000001</v>
       </c>
       <c r="F85">
-        <v>20.59230000000001</v>
+        <v>20.8404</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8629,37 +8629,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M85">
-        <v>4.855664340000001</v>
+        <v>4.914166320000001</v>
       </c>
       <c r="N85">
-        <v>-4.575664340000001</v>
+        <v>-4.63416632</v>
       </c>
       <c r="O85">
-        <v>-1.0066461548</v>
+        <v>-1.0195165904</v>
       </c>
       <c r="P85">
-        <v>-3.569018185200001</v>
+        <v>-3.6146497296</v>
       </c>
       <c r="Q85">
-        <v>-1.389018185200001</v>
+        <v>-1.4346497296</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3232594319406278</v>
+        <v>0.3406006464369171</v>
       </c>
       <c r="T85">
-        <v>6.407839074841288</v>
+        <v>6.80832901701887</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01268621463237303</v>
+        <v>0.01253518826770193</v>
       </c>
       <c r="W85">
-        <v>0.2328085905896864</v>
+        <v>0.2328442026064759</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.05766461196533201</v>
+        <v>0.0569781284895543</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8675,22 +8675,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2500852336193464</v>
+        <v>0.2519852336193464</v>
       </c>
       <c r="C86">
-        <v>-14.24365871934158</v>
+        <v>-14.54727726298326</v>
       </c>
       <c r="D86">
-        <v>6.596741280658425</v>
+        <v>6.54122273701674</v>
       </c>
       <c r="E86">
-        <v>3.740400000000001</v>
+        <v>3.988499999999998</v>
       </c>
       <c r="F86">
-        <v>20.8404</v>
+        <v>21.0885</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8711,37 +8711,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M86">
-        <v>4.914166320000001</v>
+        <v>4.9726683</v>
       </c>
       <c r="N86">
-        <v>-4.63416632</v>
+        <v>-4.692668300000001</v>
       </c>
       <c r="O86">
-        <v>-1.0195165904</v>
+        <v>-1.032387026</v>
       </c>
       <c r="P86">
-        <v>-3.6146497296</v>
+        <v>-3.660281274000001</v>
       </c>
       <c r="Q86">
-        <v>-1.4346497296</v>
+        <v>-1.480281274000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3406006464369168</v>
+        <v>0.3602540228660447</v>
       </c>
       <c r="T86">
-        <v>6.808329017018865</v>
+        <v>7.262217618153457</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01253518826770193</v>
+        <v>0.01238771546455249</v>
       </c>
       <c r="W86">
-        <v>0.2328442026064759</v>
+        <v>0.2328789766934585</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.0569781284895543</v>
+        <v>0.05630779756614757</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8757,22 +8757,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2519852336193464</v>
+        <v>0.2538852336193465</v>
       </c>
       <c r="C87">
-        <v>-14.54727726298326</v>
+        <v>-14.84996911140573</v>
       </c>
       <c r="D87">
-        <v>6.54122273701674</v>
+        <v>6.486630888594275</v>
       </c>
       <c r="E87">
-        <v>3.988499999999998</v>
+        <v>4.236599999999999</v>
       </c>
       <c r="F87">
-        <v>21.0885</v>
+        <v>21.3366</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8793,37 +8793,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M87">
-        <v>4.9726683</v>
+        <v>5.03117028</v>
       </c>
       <c r="N87">
-        <v>-4.692668300000001</v>
+        <v>-4.75117028</v>
       </c>
       <c r="O87">
-        <v>-1.032387026</v>
+        <v>-1.0452574616</v>
       </c>
       <c r="P87">
-        <v>-3.660281274000001</v>
+        <v>-3.7059128184</v>
       </c>
       <c r="Q87">
-        <v>-1.480281274000001</v>
+        <v>-1.5259128184</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3602540228660447</v>
+        <v>0.3827150244993336</v>
       </c>
       <c r="T87">
-        <v>7.262217618153457</v>
+        <v>7.780947448021561</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01238771546455249</v>
+        <v>0.0122436722614763</v>
       </c>
       <c r="W87">
-        <v>0.2328789766934585</v>
+        <v>0.2329129420807439</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.05630779756614757</v>
+        <v>0.05565305573398327</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8839,22 +8839,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2538852336193465</v>
+        <v>0.2557852336193465</v>
       </c>
       <c r="C88">
-        <v>-14.84996911140573</v>
+        <v>-15.15175727465767</v>
       </c>
       <c r="D88">
-        <v>6.486630888594275</v>
+        <v>6.432942725342331</v>
       </c>
       <c r="E88">
-        <v>4.236599999999999</v>
+        <v>4.4847</v>
       </c>
       <c r="F88">
-        <v>21.3366</v>
+        <v>21.5847</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8875,37 +8875,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M88">
-        <v>5.03117028</v>
+        <v>5.08967226</v>
       </c>
       <c r="N88">
-        <v>-4.75117028</v>
+        <v>-4.809672260000001</v>
       </c>
       <c r="O88">
-        <v>-1.0452574616</v>
+        <v>-1.0581278972</v>
       </c>
       <c r="P88">
-        <v>-3.7059128184</v>
+        <v>-3.751544362800001</v>
       </c>
       <c r="Q88">
-        <v>-1.5259128184</v>
+        <v>-1.571544362800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3827150244993336</v>
+        <v>0.4086315648454362</v>
       </c>
       <c r="T88">
-        <v>7.780947448021561</v>
+        <v>8.379481867100143</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0122436722614763</v>
+        <v>0.01210294039640186</v>
       </c>
       <c r="W88">
-        <v>0.2329129420807439</v>
+        <v>0.2329461266545285</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.05565305573398327</v>
+        <v>0.05501336543819013</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8921,22 +8921,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2557852336193465</v>
+        <v>0.2576852336193465</v>
       </c>
       <c r="C89">
-        <v>-15.15175727465767</v>
+        <v>-15.45266400724835</v>
       </c>
       <c r="D89">
-        <v>6.432942725342331</v>
+        <v>6.380135992751649</v>
       </c>
       <c r="E89">
-        <v>4.4847</v>
+        <v>4.732800000000001</v>
       </c>
       <c r="F89">
-        <v>21.5847</v>
+        <v>21.8328</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8957,37 +8957,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M89">
-        <v>5.08967226</v>
+        <v>5.14817424</v>
       </c>
       <c r="N89">
-        <v>-4.809672260000001</v>
+        <v>-4.86817424</v>
       </c>
       <c r="O89">
-        <v>-1.0581278972</v>
+        <v>-1.0709983328</v>
       </c>
       <c r="P89">
-        <v>-3.751544362800001</v>
+        <v>-3.7971759072</v>
       </c>
       <c r="Q89">
-        <v>-1.571544362800001</v>
+        <v>-1.6171759072</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4086315648454362</v>
+        <v>0.438867528582556</v>
       </c>
       <c r="T89">
-        <v>8.379481867100143</v>
+        <v>9.077772022691823</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01210294039640186</v>
+        <v>0.01196540698280638</v>
       </c>
       <c r="W89">
-        <v>0.2329461266545285</v>
+        <v>0.2329785570334543</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.05501336543819013</v>
+        <v>0.05438821355821088</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9003,22 +9003,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2576852336193465</v>
+        <v>0.2595852336193465</v>
       </c>
       <c r="C90">
-        <v>-15.45266400724835</v>
+        <v>-15.75271083890546</v>
       </c>
       <c r="D90">
-        <v>6.380135992751649</v>
+        <v>6.328189161094541</v>
       </c>
       <c r="E90">
-        <v>4.732800000000001</v>
+        <v>4.980900000000002</v>
       </c>
       <c r="F90">
-        <v>21.8328</v>
+        <v>22.0809</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -9039,37 +9039,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M90">
-        <v>5.14817424</v>
+        <v>5.206676220000001</v>
       </c>
       <c r="N90">
-        <v>-4.86817424</v>
+        <v>-4.926676220000001</v>
       </c>
       <c r="O90">
-        <v>-1.0709983328</v>
+        <v>-1.0838687684</v>
       </c>
       <c r="P90">
-        <v>-3.7971759072</v>
+        <v>-3.842807451600001</v>
       </c>
       <c r="Q90">
-        <v>-1.6171759072</v>
+        <v>-1.6628074516</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.438867528582556</v>
+        <v>0.4746009402718792</v>
       </c>
       <c r="T90">
-        <v>9.077772022691823</v>
+        <v>9.903024024754716</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01196540698280638</v>
+        <v>0.01183096420771867</v>
       </c>
       <c r="W90">
-        <v>0.2329785570334543</v>
+        <v>0.2330102586398199</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.05438821355821088</v>
+        <v>0.05377711003508501</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9085,22 +9085,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2595852336193465</v>
+        <v>0.2614852336193464</v>
       </c>
       <c r="C91">
-        <v>-15.75271083890546</v>
+        <v>-16.05191860384254</v>
       </c>
       <c r="D91">
-        <v>6.328189161094541</v>
+        <v>6.277081396157462</v>
       </c>
       <c r="E91">
-        <v>4.980900000000002</v>
+        <v>5.229000000000003</v>
       </c>
       <c r="F91">
-        <v>22.0809</v>
+        <v>22.329</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -9121,37 +9121,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M91">
-        <v>5.206676220000001</v>
+        <v>5.265178200000001</v>
       </c>
       <c r="N91">
-        <v>-4.926676220000001</v>
+        <v>-4.985178200000002</v>
       </c>
       <c r="O91">
-        <v>-1.0838687684</v>
+        <v>-1.096739204</v>
       </c>
       <c r="P91">
-        <v>-3.842807451600001</v>
+        <v>-3.888438996000001</v>
       </c>
       <c r="Q91">
-        <v>-1.6628074516</v>
+        <v>-1.708438996000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4746009402718792</v>
+        <v>0.5174810342990671</v>
       </c>
       <c r="T91">
-        <v>9.903024024754716</v>
+        <v>10.89332642723019</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01183096420771867</v>
+        <v>0.01169950904985513</v>
       </c>
       <c r="W91">
-        <v>0.2330102586398199</v>
+        <v>0.2330412557660441</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.05377711003508501</v>
+        <v>0.05317958659025046</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9167,22 +9167,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2614852336193464</v>
+        <v>0.2633852336193465</v>
       </c>
       <c r="C92">
-        <v>-16.05191860384254</v>
+        <v>-16.35030746861957</v>
       </c>
       <c r="D92">
-        <v>6.277081396157462</v>
+        <v>6.226792531380434</v>
       </c>
       <c r="E92">
-        <v>5.229000000000003</v>
+        <v>5.4771</v>
       </c>
       <c r="F92">
-        <v>22.329</v>
+        <v>22.5771</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -9203,37 +9203,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M92">
-        <v>5.265178200000001</v>
+        <v>5.32368018</v>
       </c>
       <c r="N92">
-        <v>-4.985178200000002</v>
+        <v>-5.043680180000001</v>
       </c>
       <c r="O92">
-        <v>-1.096739204</v>
+        <v>-1.1096096396</v>
       </c>
       <c r="P92">
-        <v>-3.888438996000001</v>
+        <v>-3.9340705404</v>
       </c>
       <c r="Q92">
-        <v>-1.708438996000001</v>
+        <v>-1.7540705404</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5174810342990671</v>
+        <v>0.5698900381100747</v>
       </c>
       <c r="T92">
-        <v>10.89332642723019</v>
+        <v>12.10369603025577</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01169950904985513</v>
+        <v>0.01157094301634024</v>
       </c>
       <c r="W92">
-        <v>0.2330412557660441</v>
+        <v>0.233071571636747</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.05317958659025046</v>
+        <v>0.05259519552881919</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9249,22 +9249,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2633852336193465</v>
+        <v>0.2652852336193465</v>
       </c>
       <c r="C93">
-        <v>-16.35030746861957</v>
+        <v>-16.64789695867495</v>
       </c>
       <c r="D93">
-        <v>6.226792531380434</v>
+        <v>6.177303041325055</v>
       </c>
       <c r="E93">
-        <v>5.4771</v>
+        <v>5.725200000000001</v>
       </c>
       <c r="F93">
-        <v>22.5771</v>
+        <v>22.8252</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -9285,37 +9285,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M93">
-        <v>5.32368018</v>
+        <v>5.382182160000001</v>
       </c>
       <c r="N93">
-        <v>-5.043680180000001</v>
+        <v>-5.102182160000002</v>
       </c>
       <c r="O93">
-        <v>-1.1096096396</v>
+        <v>-1.1224800752</v>
       </c>
       <c r="P93">
-        <v>-3.9340705404</v>
+        <v>-3.979702084800001</v>
       </c>
       <c r="Q93">
-        <v>-1.7540705404</v>
+        <v>-1.799702084800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5698900381100747</v>
+        <v>0.6354012928738341</v>
       </c>
       <c r="T93">
-        <v>12.10369603025577</v>
+        <v>13.61665803403774</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01157094301634024</v>
+        <v>0.01144517189659741</v>
       </c>
       <c r="W93">
-        <v>0.233071571636747</v>
+        <v>0.2331012284667823</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.05259519552881919</v>
+        <v>0.05202350862089722</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9331,22 +9331,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2652852336193465</v>
+        <v>0.2671852336193464</v>
       </c>
       <c r="C94">
-        <v>-16.64789695867495</v>
+        <v>-16.94470598360222</v>
       </c>
       <c r="D94">
-        <v>6.177303041325055</v>
+        <v>6.128594016397782</v>
       </c>
       <c r="E94">
-        <v>5.725200000000001</v>
+        <v>5.973300000000002</v>
       </c>
       <c r="F94">
-        <v>22.8252</v>
+        <v>23.0733</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -9367,37 +9367,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M94">
-        <v>5.382182160000001</v>
+        <v>5.440684140000001</v>
       </c>
       <c r="N94">
-        <v>-5.102182160000002</v>
+        <v>-5.160684140000001</v>
       </c>
       <c r="O94">
-        <v>-1.1224800752</v>
+        <v>-1.1353505108</v>
       </c>
       <c r="P94">
-        <v>-3.979702084800001</v>
+        <v>-4.0253336292</v>
       </c>
       <c r="Q94">
-        <v>-1.799702084800001</v>
+        <v>-1.8453336292</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6354012928738341</v>
+        <v>0.7196300489986676</v>
       </c>
       <c r="T94">
-        <v>13.61665803403774</v>
+        <v>15.56189489604313</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01144517189659741</v>
+        <v>0.01132210553211787</v>
       </c>
       <c r="W94">
-        <v>0.2331012284667823</v>
+        <v>0.2331302475155266</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.05202350862089722</v>
+        <v>0.05146411605508128</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9413,22 +9413,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2671852336193464</v>
+        <v>0.2690852336193464</v>
       </c>
       <c r="C95">
-        <v>-16.94470598360222</v>
+        <v>-17.24075286124031</v>
       </c>
       <c r="D95">
-        <v>6.128594016397782</v>
+        <v>6.080647138759695</v>
       </c>
       <c r="E95">
-        <v>5.973300000000002</v>
+        <v>6.221400000000003</v>
       </c>
       <c r="F95">
-        <v>23.0733</v>
+        <v>23.3214</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9449,37 +9449,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M95">
-        <v>5.440684140000001</v>
+        <v>5.499186120000001</v>
       </c>
       <c r="N95">
-        <v>-5.160684140000001</v>
+        <v>-5.219186120000002</v>
       </c>
       <c r="O95">
-        <v>-1.1353505108</v>
+        <v>-1.1482209464</v>
       </c>
       <c r="P95">
-        <v>-4.0253336292</v>
+        <v>-4.070965173600001</v>
       </c>
       <c r="Q95">
-        <v>-1.8453336292</v>
+        <v>-1.890965173600001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7196300489986676</v>
+        <v>0.8319350571651124</v>
       </c>
       <c r="T95">
-        <v>15.56189489604313</v>
+        <v>18.15554404538366</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01132210553211787</v>
+        <v>0.01120165760092512</v>
       </c>
       <c r="W95">
-        <v>0.2331302475155266</v>
+        <v>0.2331586491377018</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.05146411605508128</v>
+        <v>0.05091662545875053</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9495,22 +9495,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2690852336193464</v>
+        <v>0.2709852336193465</v>
       </c>
       <c r="C96">
-        <v>-17.24075286124031</v>
+        <v>-17.53605534064169</v>
       </c>
       <c r="D96">
-        <v>6.080647138759695</v>
+        <v>6.033444659358316</v>
       </c>
       <c r="E96">
-        <v>6.221400000000003</v>
+        <v>6.469500000000004</v>
       </c>
       <c r="F96">
-        <v>23.3214</v>
+        <v>23.56950000000001</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9531,37 +9531,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M96">
-        <v>5.499186120000001</v>
+        <v>5.557688100000002</v>
       </c>
       <c r="N96">
-        <v>-5.219186120000002</v>
+        <v>-5.277688100000002</v>
       </c>
       <c r="O96">
-        <v>-1.1482209464</v>
+        <v>-1.161091382000001</v>
       </c>
       <c r="P96">
-        <v>-4.070965173600001</v>
+        <v>-4.116596718000002</v>
       </c>
       <c r="Q96">
-        <v>-1.890965173600001</v>
+        <v>-1.936596718000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8319350571651124</v>
+        <v>0.9891620685981354</v>
       </c>
       <c r="T96">
-        <v>18.15554404538366</v>
+        <v>21.7866528544604</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01120165760092512</v>
+        <v>0.01108374541565223</v>
       </c>
       <c r="W96">
-        <v>0.2331586491377018</v>
+        <v>0.2331864528309892</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.05091662545875053</v>
+        <v>0.0503806609802373</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9577,22 +9577,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2709852336193465</v>
+        <v>0.2728852336193465</v>
       </c>
       <c r="C97">
-        <v>-17.53605534064169</v>
+        <v>-17.83063062397904</v>
       </c>
       <c r="D97">
-        <v>6.033444659358316</v>
+        <v>5.986969376020965</v>
       </c>
       <c r="E97">
-        <v>6.469500000000004</v>
+        <v>6.717600000000001</v>
       </c>
       <c r="F97">
-        <v>23.56950000000001</v>
+        <v>23.8176</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9613,37 +9613,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M97">
-        <v>5.557688100000002</v>
+        <v>5.616190080000001</v>
       </c>
       <c r="N97">
-        <v>-5.277688100000002</v>
+        <v>-5.336190080000002</v>
       </c>
       <c r="O97">
-        <v>-1.161091382000001</v>
+        <v>-1.1739618176</v>
       </c>
       <c r="P97">
-        <v>-4.116596718000002</v>
+        <v>-4.162228262400001</v>
       </c>
       <c r="Q97">
-        <v>-1.936596718000002</v>
+        <v>-1.982228262400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9891620685981354</v>
+        <v>1.22500258574767</v>
       </c>
       <c r="T97">
-        <v>21.7866528544604</v>
+        <v>27.23331606807552</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01108374541565223</v>
+        <v>0.01096828973423918</v>
       </c>
       <c r="W97">
-        <v>0.2331864528309892</v>
+        <v>0.2332136772806664</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.0503806609802373</v>
+        <v>0.04985586242835982</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9659,22 +9659,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2728852336193465</v>
+        <v>0.2747852336193465</v>
       </c>
       <c r="C98">
-        <v>-17.83063062397904</v>
+        <v>-18.12449538744717</v>
       </c>
       <c r="D98">
-        <v>5.986969376020965</v>
+        <v>5.941204612552834</v>
       </c>
       <c r="E98">
-        <v>6.717600000000001</v>
+        <v>6.965700000000002</v>
       </c>
       <c r="F98">
-        <v>23.8176</v>
+        <v>24.0657</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9695,37 +9695,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M98">
-        <v>5.616190080000001</v>
+        <v>5.674692060000001</v>
       </c>
       <c r="N98">
-        <v>-5.336190080000002</v>
+        <v>-5.394692060000001</v>
       </c>
       <c r="O98">
-        <v>-1.1739618176</v>
+        <v>-1.1868322532</v>
       </c>
       <c r="P98">
-        <v>-4.162228262400001</v>
+        <v>-4.2078598068</v>
       </c>
       <c r="Q98">
-        <v>-1.982228262400001</v>
+        <v>-2.0278598068</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.225002585747667</v>
+        <v>1.618070114330223</v>
       </c>
       <c r="T98">
-        <v>27.23331606807545</v>
+        <v>36.31108809076726</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01096828973423918</v>
+        <v>0.01085521458233981</v>
       </c>
       <c r="W98">
-        <v>0.2332136772806664</v>
+        <v>0.2332403404014843</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.04985586242835982</v>
+        <v>0.04934188446518106</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9741,22 +9741,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2747852336193465</v>
+        <v>0.2766852336193464</v>
       </c>
       <c r="C99">
-        <v>-18.12449538744717</v>
+        <v>-18.41766580121352</v>
       </c>
       <c r="D99">
-        <v>5.941204612552834</v>
+        <v>5.896134198786477</v>
       </c>
       <c r="E99">
-        <v>6.965700000000002</v>
+        <v>7.213799999999999</v>
       </c>
       <c r="F99">
-        <v>24.0657</v>
+        <v>24.3138</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9777,37 +9777,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M99">
-        <v>5.674692060000001</v>
+        <v>5.733194040000001</v>
       </c>
       <c r="N99">
-        <v>-5.394692060000001</v>
+        <v>-5.453194040000001</v>
       </c>
       <c r="O99">
-        <v>-1.1868322532</v>
+        <v>-1.1997026888</v>
       </c>
       <c r="P99">
-        <v>-4.2078598068</v>
+        <v>-4.253491351200001</v>
       </c>
       <c r="Q99">
-        <v>-2.0278598068</v>
+        <v>-2.073491351200001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.618070114330223</v>
+        <v>2.404205171495333</v>
       </c>
       <c r="T99">
-        <v>36.31108809076726</v>
+        <v>54.46663213615089</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01085521458233981</v>
+        <v>0.01074444708660165</v>
       </c>
       <c r="W99">
-        <v>0.2332403404014843</v>
+        <v>0.2332664593769793</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.04934188446518106</v>
+        <v>0.04883839584818928</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9823,22 +9823,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2766852336193464</v>
+        <v>0.2785852336193465</v>
       </c>
       <c r="C100">
-        <v>-18.41766580121352</v>
+        <v>-18.71015754846753</v>
       </c>
       <c r="D100">
-        <v>5.896134198786477</v>
+        <v>5.851742451532475</v>
       </c>
       <c r="E100">
-        <v>7.213799999999999</v>
+        <v>7.4619</v>
       </c>
       <c r="F100">
-        <v>24.3138</v>
+        <v>24.5619</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9859,37 +9859,37 @@
         <v>0.2799999999999998</v>
       </c>
       <c r="M100">
-        <v>5.733194040000001</v>
+        <v>5.791696020000001</v>
       </c>
       <c r="N100">
-        <v>-5.453194040000001</v>
+        <v>-5.51169602</v>
       </c>
       <c r="O100">
-        <v>-1.1997026888</v>
+        <v>-1.2125731244</v>
       </c>
       <c r="P100">
-        <v>-4.253491351200001</v>
+        <v>-4.2991228956</v>
       </c>
       <c r="Q100">
-        <v>-2.073491351200001</v>
+        <v>-2.1191228956</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.404205171495333</v>
+        <v>4.762610342990667</v>
       </c>
       <c r="T100">
-        <v>54.46663213615089</v>
+        <v>108.9332642723018</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01074444708660165</v>
+        <v>0.01063591731805012</v>
       </c>
       <c r="W100">
-        <v>0.2332664593769793</v>
+        <v>0.2332920506964038</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9897,91 +9897,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.04883839584818928</v>
+        <v>0.04834507871840976</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2785852336193465</v>
-      </c>
-      <c r="C101">
-        <v>-18.71015754846753</v>
-      </c>
-      <c r="D101">
-        <v>5.851742451532475</v>
-      </c>
-      <c r="E101">
-        <v>7.4619</v>
-      </c>
-      <c r="F101">
-        <v>24.5619</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>7.71</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.46</v>
-      </c>
-      <c r="K101">
-        <v>2.18</v>
-      </c>
-      <c r="L101">
-        <v>0.2799999999999998</v>
-      </c>
-      <c r="M101">
-        <v>5.791696020000001</v>
-      </c>
-      <c r="N101">
-        <v>-5.51169602</v>
-      </c>
-      <c r="O101">
-        <v>-1.2125731244</v>
-      </c>
-      <c r="P101">
-        <v>-4.2991228956</v>
-      </c>
-      <c r="Q101">
-        <v>-2.1191228956</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.762610342990667</v>
-      </c>
-      <c r="T101">
-        <v>108.9332642723018</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01063591731805012</v>
-      </c>
-      <c r="W101">
-        <v>0.2332920506964038</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.04834507871840976</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
